--- a/副本-ysyx_-张三-xx大学-学习记录.xlsx
+++ b/副本-ysyx_-张三-xx大学-学习记录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OSOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6AF117-F4D0-4026-84B4-ED31025EB3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787CFD2D-1A08-495B-806D-D9935663095F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学习记录表格（模板）" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="698">
   <si>
     <t>ysyx_22040088-吴佳宾-青岛大学-学习记录（从零开始）</t>
   </si>
@@ -4075,6 +4075,42 @@
   </si>
   <si>
     <t>大部分比较熟悉</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>5h</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成F5的学习</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.00-20.00</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成F5的前一节学习</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试搭建ROM,RAM</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.00-16.00</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>3h</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试搭建sCPU</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>加法多端口遇到困难</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -4553,6 +4589,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4561,9 +4621,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4598,15 +4655,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4627,18 +4675,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4957,67 +4993,67 @@
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" customWidth="1"/>
-    <col min="2" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.08203125" customWidth="1"/>
-    <col min="6" max="6" width="8.08203125" customWidth="1"/>
-    <col min="7" max="7" width="32.5" customWidth="1"/>
-    <col min="8" max="8" width="32.75" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="63.25" customWidth="1"/>
-    <col min="11" max="12" width="11.58203125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="34.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" customWidth="1"/>
+    <col min="6" max="6" width="8.08984375" customWidth="1"/>
+    <col min="7" max="7" width="32.453125" customWidth="1"/>
+    <col min="8" max="8" width="32.7265625" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="63.26953125" customWidth="1"/>
+    <col min="11" max="12" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12.45">
+    <row r="1" spans="1:12">
       <c r="A1" s="24"/>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="63" t="s">
         <v>576</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
       <c r="J1" s="24"/>
       <c r="K1" s="24"/>
       <c r="L1" s="24"/>
     </row>
-    <row r="2" spans="1:12" ht="12.45">
+    <row r="2" spans="1:12">
       <c r="A2" s="24"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
       <c r="L2" s="24"/>
     </row>
-    <row r="3" spans="1:12" ht="12.45">
+    <row r="3" spans="1:12">
       <c r="A3" s="24"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
     </row>
-    <row r="4" spans="1:12" ht="12.45">
+    <row r="4" spans="1:12">
       <c r="A4" s="35"/>
       <c r="B4" s="36" t="s">
         <v>1</v>
@@ -5049,128 +5085,156 @@
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
     </row>
-    <row r="5" spans="1:12" ht="23.15">
-      <c r="A5" s="76" t="s">
+    <row r="5" spans="1:12">
+      <c r="A5" s="65" t="s">
         <v>579</v>
       </c>
       <c r="B5" s="38">
         <v>46121</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="59" t="s">
         <v>670</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="62" t="s">
         <v>672</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="60" t="s">
         <v>673</v>
       </c>
-      <c r="F5" s="84" t="s">
+      <c r="F5" s="59" t="s">
         <v>670</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="G5" s="59" t="s">
         <v>675</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="61" t="s">
         <v>676</v>
       </c>
       <c r="I5" s="35"/>
-      <c r="J5" s="86" t="s">
+      <c r="J5" s="61" t="s">
         <v>677</v>
       </c>
       <c r="K5" s="35"/>
       <c r="L5" s="35"/>
     </row>
-    <row r="6" spans="1:12" ht="12.45">
-      <c r="A6" s="62"/>
+    <row r="6" spans="1:12">
+      <c r="A6" s="66"/>
       <c r="B6" s="38">
         <v>46122</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="59" t="s">
         <v>678</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="59" t="s">
         <v>684</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="59" t="s">
         <v>680</v>
       </c>
-      <c r="F6" s="84" t="s">
+      <c r="F6" s="59" t="s">
         <v>681</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="H6" s="61" t="s">
         <v>676</v>
       </c>
       <c r="I6" s="35"/>
-      <c r="J6" s="86" t="s">
+      <c r="J6" s="61" t="s">
         <v>683</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35"/>
     </row>
     <row r="7" spans="1:12" ht="33" customHeight="1">
-      <c r="A7" s="62"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="38">
         <v>46123</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="59" t="s">
         <v>678</v>
       </c>
-      <c r="D7" s="84" t="s">
+      <c r="D7" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="E7" s="84" t="s">
+      <c r="E7" s="59" t="s">
         <v>686</v>
       </c>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="59" t="s">
         <v>679</v>
       </c>
-      <c r="G7" s="87" t="s">
+      <c r="G7" s="62" t="s">
         <v>687</v>
       </c>
-      <c r="H7" s="86" t="s">
+      <c r="H7" s="61" t="s">
         <v>676</v>
       </c>
       <c r="I7" s="35"/>
-      <c r="J7" s="86" t="s">
+      <c r="J7" s="61" t="s">
         <v>688</v>
       </c>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="35"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="38">
+        <v>46124</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>689</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>692</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>691</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>689</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>693</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>676</v>
+      </c>
       <c r="I8" s="35"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
     </row>
     <row r="9" spans="1:12" ht="19" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="35"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="38">
+        <v>46127</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>689</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>690</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>694</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>695</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>696</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>697</v>
+      </c>
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
     </row>
     <row r="10" spans="1:12" ht="19" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="38"/>
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
@@ -5183,8 +5247,8 @@
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
     </row>
-    <row r="11" spans="1:12" ht="12.45">
-      <c r="A11" s="62"/>
+    <row r="11" spans="1:12">
+      <c r="A11" s="66"/>
       <c r="B11" s="38"/>
       <c r="C11" s="39"/>
       <c r="D11" s="39"/>
@@ -5197,8 +5261,8 @@
       <c r="K11" s="35"/>
       <c r="L11" s="35"/>
     </row>
-    <row r="12" spans="1:12" ht="12.45">
-      <c r="A12" s="76" t="s">
+    <row r="12" spans="1:12">
+      <c r="A12" s="65" t="s">
         <v>580</v>
       </c>
       <c r="B12" s="38"/>
@@ -5213,8 +5277,8 @@
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
     </row>
-    <row r="13" spans="1:12" ht="12.45">
-      <c r="A13" s="62"/>
+    <row r="13" spans="1:12">
+      <c r="A13" s="66"/>
       <c r="B13" s="38"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -5227,8 +5291,8 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="1:12" ht="12.45">
-      <c r="A14" s="62"/>
+    <row r="14" spans="1:12">
+      <c r="A14" s="66"/>
       <c r="B14" s="38"/>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -5241,8 +5305,8 @@
       <c r="K14" s="35"/>
       <c r="L14" s="35"/>
     </row>
-    <row r="15" spans="1:12" ht="12.45">
-      <c r="A15" s="62"/>
+    <row r="15" spans="1:12">
+      <c r="A15" s="66"/>
       <c r="B15" s="38"/>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
@@ -5255,8 +5319,8 @@
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
     </row>
-    <row r="16" spans="1:12" ht="12.45">
-      <c r="A16" s="62"/>
+    <row r="16" spans="1:12">
+      <c r="A16" s="66"/>
       <c r="B16" s="38"/>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
@@ -5269,8 +5333,8 @@
       <c r="K16" s="35"/>
       <c r="L16" s="35"/>
     </row>
-    <row r="17" spans="1:12" ht="12.45">
-      <c r="A17" s="62"/>
+    <row r="17" spans="1:12">
+      <c r="A17" s="66"/>
       <c r="B17" s="38"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
@@ -5283,8 +5347,8 @@
       <c r="K17" s="35"/>
       <c r="L17" s="35"/>
     </row>
-    <row r="18" spans="1:12" ht="12.45">
-      <c r="A18" s="62"/>
+    <row r="18" spans="1:12">
+      <c r="A18" s="66"/>
       <c r="B18" s="38"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -5297,8 +5361,8 @@
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
     </row>
-    <row r="19" spans="1:12" ht="12.45">
-      <c r="A19" s="76" t="s">
+    <row r="19" spans="1:12">
+      <c r="A19" s="65" t="s">
         <v>581</v>
       </c>
       <c r="B19" s="38"/>
@@ -5313,8 +5377,8 @@
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
     </row>
-    <row r="20" spans="1:12" ht="12.45">
-      <c r="A20" s="62"/>
+    <row r="20" spans="1:12">
+      <c r="A20" s="66"/>
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -5327,8 +5391,8 @@
       <c r="K20" s="35"/>
       <c r="L20" s="35"/>
     </row>
-    <row r="21" spans="1:12" ht="12.45">
-      <c r="A21" s="62"/>
+    <row r="21" spans="1:12">
+      <c r="A21" s="66"/>
       <c r="B21" s="38"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -5341,8 +5405,8 @@
       <c r="K21" s="35"/>
       <c r="L21" s="35"/>
     </row>
-    <row r="22" spans="1:12" ht="12.45">
-      <c r="A22" s="62"/>
+    <row r="22" spans="1:12">
+      <c r="A22" s="66"/>
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -5356,7 +5420,7 @@
       <c r="L22" s="35"/>
     </row>
     <row r="23" spans="1:12" ht="19" customHeight="1">
-      <c r="A23" s="62"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="38"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -5370,7 +5434,7 @@
       <c r="L23" s="35"/>
     </row>
     <row r="24" spans="1:12" ht="19" customHeight="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -5383,8 +5447,8 @@
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
     </row>
-    <row r="25" spans="1:12" ht="12.45">
-      <c r="A25" s="62"/>
+    <row r="25" spans="1:12">
+      <c r="A25" s="66"/>
       <c r="B25" s="38"/>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -5397,7 +5461,7 @@
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" ht="14">
       <c r="A26" s="24"/>
       <c r="B26" s="40"/>
       <c r="C26" s="24"/>
@@ -5411,7 +5475,7 @@
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" ht="14">
       <c r="A27" s="24"/>
       <c r="B27" s="24"/>
       <c r="C27" s="24"/>
@@ -5425,7 +5489,7 @@
       <c r="K27" s="24"/>
       <c r="L27" s="24"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" ht="14">
       <c r="A28" s="24"/>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -5439,7 +5503,7 @@
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" ht="14">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -5453,178 +5517,6 @@
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
     </row>
-    <row r="30" spans="1:12" ht="12.45"/>
-    <row r="31" spans="1:12" ht="12.45"/>
-    <row r="32" spans="1:12" ht="12.45"/>
-    <row r="33" ht="12.45"/>
-    <row r="34" ht="12.45"/>
-    <row r="35" ht="12.45"/>
-    <row r="36" ht="12.45"/>
-    <row r="37" ht="12.45"/>
-    <row r="38" ht="12.45"/>
-    <row r="39" ht="12.45"/>
-    <row r="40" ht="12.45"/>
-    <row r="41" ht="12.45"/>
-    <row r="42" ht="12.45"/>
-    <row r="43" ht="12.45"/>
-    <row r="44" ht="12.45"/>
-    <row r="45" ht="12.45"/>
-    <row r="46" ht="12.45"/>
-    <row r="47" ht="12.45"/>
-    <row r="48" ht="12.45"/>
-    <row r="49" ht="12.45"/>
-    <row r="50" ht="12.45"/>
-    <row r="51" ht="12.45"/>
-    <row r="52" ht="12.45"/>
-    <row r="53" ht="12.45"/>
-    <row r="54" ht="12.45"/>
-    <row r="55" ht="12.45"/>
-    <row r="56" ht="12.45"/>
-    <row r="57" ht="12.45"/>
-    <row r="58" ht="12.45"/>
-    <row r="59" ht="12.45"/>
-    <row r="60" ht="12.45"/>
-    <row r="61" ht="12.45"/>
-    <row r="62" ht="12.45"/>
-    <row r="63" ht="12.45"/>
-    <row r="64" ht="12.45"/>
-    <row r="65" ht="12.45"/>
-    <row r="66" ht="12.45"/>
-    <row r="67" ht="12.45"/>
-    <row r="68" ht="12.45"/>
-    <row r="69" ht="12.45"/>
-    <row r="70" ht="12.45"/>
-    <row r="71" ht="12.45"/>
-    <row r="72" ht="12.45"/>
-    <row r="73" ht="12.45"/>
-    <row r="74" ht="12.45"/>
-    <row r="75" ht="12.45"/>
-    <row r="76" ht="12.45"/>
-    <row r="77" ht="12.45"/>
-    <row r="78" ht="12.45"/>
-    <row r="79" ht="12.45"/>
-    <row r="80" ht="12.45"/>
-    <row r="81" ht="12.45"/>
-    <row r="82" ht="12.45"/>
-    <row r="83" ht="12.45"/>
-    <row r="84" ht="12.45"/>
-    <row r="85" ht="12.45"/>
-    <row r="86" ht="12.45"/>
-    <row r="87" ht="12.45"/>
-    <row r="88" ht="12.45"/>
-    <row r="89" ht="12.45"/>
-    <row r="90" ht="12.45"/>
-    <row r="91" ht="12.45"/>
-    <row r="92" ht="12.45"/>
-    <row r="93" ht="12.45"/>
-    <row r="94" ht="12.45"/>
-    <row r="95" ht="12.45"/>
-    <row r="96" ht="12.45"/>
-    <row r="97" ht="12.45"/>
-    <row r="98" ht="12.45"/>
-    <row r="99" ht="12.45"/>
-    <row r="100" ht="12.45"/>
-    <row r="101" ht="12.45"/>
-    <row r="102" ht="12.45"/>
-    <row r="103" ht="12.45"/>
-    <row r="104" ht="12.45"/>
-    <row r="105" ht="12.45"/>
-    <row r="106" ht="12.45"/>
-    <row r="107" ht="12.45"/>
-    <row r="108" ht="12.45"/>
-    <row r="109" ht="12.45"/>
-    <row r="110" ht="12.45"/>
-    <row r="111" ht="12.45"/>
-    <row r="112" ht="12.45"/>
-    <row r="113" ht="12.45"/>
-    <row r="114" ht="12.45"/>
-    <row r="115" ht="12.45"/>
-    <row r="116" ht="12.45"/>
-    <row r="117" ht="12.45"/>
-    <row r="118" ht="12.45"/>
-    <row r="119" ht="12.45"/>
-    <row r="120" ht="12.45"/>
-    <row r="121" ht="12.45"/>
-    <row r="122" ht="12.45"/>
-    <row r="123" ht="12.45"/>
-    <row r="124" ht="12.45"/>
-    <row r="125" ht="12.45"/>
-    <row r="126" ht="12.45"/>
-    <row r="127" ht="12.45"/>
-    <row r="128" ht="12.45"/>
-    <row r="129" ht="12.45"/>
-    <row r="130" ht="12.45"/>
-    <row r="131" ht="12.45"/>
-    <row r="132" ht="12.45"/>
-    <row r="133" ht="12.45"/>
-    <row r="134" ht="12.45"/>
-    <row r="135" ht="12.45"/>
-    <row r="136" ht="12.45"/>
-    <row r="137" ht="12.45"/>
-    <row r="138" ht="12.45"/>
-    <row r="139" ht="12.45"/>
-    <row r="140" ht="12.45"/>
-    <row r="141" ht="12.45"/>
-    <row r="142" ht="12.45"/>
-    <row r="143" ht="12.45"/>
-    <row r="144" ht="12.45"/>
-    <row r="145" ht="12.45"/>
-    <row r="146" ht="12.45"/>
-    <row r="147" ht="12.45"/>
-    <row r="148" ht="12.45"/>
-    <row r="149" ht="12.45"/>
-    <row r="150" ht="12.45"/>
-    <row r="151" ht="12.45"/>
-    <row r="152" ht="12.45"/>
-    <row r="153" ht="12.45"/>
-    <row r="154" ht="12.45"/>
-    <row r="155" ht="12.45"/>
-    <row r="156" ht="12.45"/>
-    <row r="157" ht="12.45"/>
-    <row r="158" ht="12.45"/>
-    <row r="159" ht="12.45"/>
-    <row r="160" ht="12.45"/>
-    <row r="161" ht="12.45"/>
-    <row r="162" ht="12.45"/>
-    <row r="163" ht="12.45"/>
-    <row r="164" ht="12.45"/>
-    <row r="165" ht="12.45"/>
-    <row r="166" ht="12.45"/>
-    <row r="167" ht="12.45"/>
-    <row r="168" ht="12.45"/>
-    <row r="169" ht="12.45"/>
-    <row r="170" ht="12.45"/>
-    <row r="171" ht="12.45"/>
-    <row r="172" ht="12.45"/>
-    <row r="173" ht="12.45"/>
-    <row r="174" ht="12.45"/>
-    <row r="175" ht="12.45"/>
-    <row r="176" ht="12.45"/>
-    <row r="177" ht="12.45"/>
-    <row r="178" ht="12.45"/>
-    <row r="179" ht="12.45"/>
-    <row r="180" ht="12.45"/>
-    <row r="181" ht="12.45"/>
-    <row r="182" ht="12.45"/>
-    <row r="183" ht="12.45"/>
-    <row r="184" ht="12.45"/>
-    <row r="185" ht="12.45"/>
-    <row r="186" ht="12.45"/>
-    <row r="187" ht="12.45"/>
-    <row r="188" ht="12.45"/>
-    <row r="189" ht="12.45"/>
-    <row r="190" ht="12.45"/>
-    <row r="191" ht="12.45"/>
-    <row r="192" ht="12.45"/>
-    <row r="193" ht="12.45"/>
-    <row r="194" ht="12.45"/>
-    <row r="195" ht="12.45"/>
-    <row r="196" ht="12.45"/>
-    <row r="197" ht="12.45"/>
-    <row r="198" ht="12.45"/>
-    <row r="199" ht="12.45"/>
-    <row r="200" ht="12.45"/>
-    <row r="201" ht="12.45"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:I3"/>
@@ -5643,40 +5535,40 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:L228"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" customWidth="1"/>
-    <col min="2" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-    <col min="4" max="4" width="7.58203125" customWidth="1"/>
-    <col min="5" max="5" width="56.6640625" customWidth="1"/>
-    <col min="6" max="6" width="51.1640625" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="63.25" customWidth="1"/>
-    <col min="9" max="12" width="11.58203125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="5" width="56.6328125" customWidth="1"/>
+    <col min="6" max="6" width="51.1796875" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" customWidth="1"/>
+    <col min="8" max="8" width="63.26953125" customWidth="1"/>
+    <col min="9" max="12" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="14">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
       <c r="G1" s="2"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" ht="14">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
       <c r="G2" s="2"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -5722,8 +5614,8 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="23.15">
-      <c r="A5" s="61" t="s">
+    <row r="5" spans="1:12" ht="24">
+      <c r="A5" s="69" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="12">
@@ -5750,8 +5642,8 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="12.45">
-      <c r="A6" s="62"/>
+    <row r="6" spans="1:12">
+      <c r="A6" s="66"/>
       <c r="B6" s="12">
         <v>44938</v>
       </c>
@@ -5777,7 +5669,7 @@
       <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" ht="33" customHeight="1">
-      <c r="A7" s="62"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="12">
         <v>44939</v>
       </c>
@@ -5803,7 +5695,7 @@
       <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:12" ht="33" customHeight="1">
-      <c r="A8" s="62"/>
+      <c r="A8" s="66"/>
       <c r="B8" s="12">
         <v>44942</v>
       </c>
@@ -5825,7 +5717,7 @@
       <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:12" ht="19" customHeight="1">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="69" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="12">
@@ -5853,7 +5745,7 @@
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" ht="19" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="12">
         <v>44944</v>
       </c>
@@ -5878,8 +5770,8 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="12.45">
-      <c r="A11" s="62"/>
+    <row r="11" spans="1:12">
+      <c r="A11" s="66"/>
       <c r="B11" s="12">
         <v>44946</v>
       </c>
@@ -5905,7 +5797,7 @@
       <c r="L11" s="11"/>
     </row>
     <row r="12" spans="1:12" ht="19" customHeight="1">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="69" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="12">
@@ -5932,8 +5824,8 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="12.45">
-      <c r="A13" s="62"/>
+    <row r="13" spans="1:12">
+      <c r="A13" s="66"/>
       <c r="B13" s="12">
         <v>44953</v>
       </c>
@@ -5956,8 +5848,8 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="12.45">
-      <c r="A14" s="62"/>
+    <row r="14" spans="1:12">
+      <c r="A14" s="66"/>
       <c r="B14" s="12">
         <v>44954</v>
       </c>
@@ -5982,8 +5874,8 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="12.45">
-      <c r="A15" s="61" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="69" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="12">
@@ -6010,8 +5902,8 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="12.45">
-      <c r="A16" s="62"/>
+    <row r="16" spans="1:12">
+      <c r="A16" s="66"/>
       <c r="B16" s="12">
         <v>44968</v>
       </c>
@@ -6034,8 +5926,8 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
     </row>
-    <row r="17" spans="1:12" ht="12.45">
-      <c r="A17" s="62"/>
+    <row r="17" spans="1:12">
+      <c r="A17" s="66"/>
       <c r="B17" s="12">
         <v>44969</v>
       </c>
@@ -6057,7 +5949,7 @@
       <c r="L17" s="11"/>
     </row>
     <row r="18" spans="1:12" ht="33" customHeight="1">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="70" t="s">
         <v>52</v>
       </c>
       <c r="B18" s="12">
@@ -6082,8 +5974,8 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" ht="12.45">
-      <c r="A19" s="64"/>
+    <row r="19" spans="1:12">
+      <c r="A19" s="71"/>
       <c r="B19" s="12">
         <v>44979</v>
       </c>
@@ -6107,7 +5999,7 @@
       <c r="L19" s="11"/>
     </row>
     <row r="20" spans="1:12" ht="37" customHeight="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="12">
         <v>44980</v>
       </c>
@@ -6133,7 +6025,7 @@
       <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12" ht="67" customHeight="1">
-      <c r="A21" s="64"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="12">
         <v>44981</v>
       </c>
@@ -6159,7 +6051,7 @@
       <c r="L21" s="11"/>
     </row>
     <row r="22" spans="1:12" ht="33" customHeight="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="12">
         <v>44982</v>
       </c>
@@ -6185,7 +6077,7 @@
       <c r="L22" s="11"/>
     </row>
     <row r="23" spans="1:12" ht="33" customHeight="1">
-      <c r="A23" s="64"/>
+      <c r="A23" s="71"/>
       <c r="B23" s="12">
         <v>44983</v>
       </c>
@@ -6210,8 +6102,8 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
-    <row r="24" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A24" s="64"/>
+    <row r="24" spans="1:12" ht="50" customHeight="1">
+      <c r="A24" s="71"/>
       <c r="B24" s="12">
         <v>44984</v>
       </c>
@@ -6237,7 +6129,7 @@
       <c r="L24" s="11"/>
     </row>
     <row r="25" spans="1:12" ht="33" customHeight="1">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="70" t="s">
         <v>77</v>
       </c>
       <c r="B25" s="12">
@@ -6264,8 +6156,8 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
     </row>
-    <row r="26" spans="1:12" ht="12.45">
-      <c r="A26" s="64"/>
+    <row r="26" spans="1:12">
+      <c r="A26" s="71"/>
       <c r="B26" s="21">
         <v>44986</v>
       </c>
@@ -6286,8 +6178,8 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:12" ht="23.15">
-      <c r="A27" s="64"/>
+    <row r="27" spans="1:12" ht="24">
+      <c r="A27" s="71"/>
       <c r="B27" s="21">
         <v>44987</v>
       </c>
@@ -6311,7 +6203,7 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:12" ht="67" customHeight="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="21">
         <v>44988</v>
       </c>
@@ -6332,8 +6224,8 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A29" s="64"/>
+    <row r="29" spans="1:12" ht="50" customHeight="1">
+      <c r="A29" s="71"/>
       <c r="B29" s="21">
         <v>44989</v>
       </c>
@@ -6356,8 +6248,8 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:12" ht="23.15">
-      <c r="A30" s="64"/>
+    <row r="30" spans="1:12" ht="24">
+      <c r="A30" s="71"/>
       <c r="B30" s="21">
         <v>44990</v>
       </c>
@@ -6382,8 +6274,8 @@
       <c r="K30" s="24"/>
       <c r="L30" s="24"/>
     </row>
-    <row r="31" spans="1:12" ht="23.15">
-      <c r="A31" s="64"/>
+    <row r="31" spans="1:12" ht="24">
+      <c r="A31" s="71"/>
       <c r="B31" s="21">
         <v>44991</v>
       </c>
@@ -6408,8 +6300,8 @@
       <c r="K31" s="24"/>
       <c r="L31" s="24"/>
     </row>
-    <row r="32" spans="1:12" ht="23.15">
-      <c r="A32" s="63" t="s">
+    <row r="32" spans="1:12" ht="24">
+      <c r="A32" s="70" t="s">
         <v>100</v>
       </c>
       <c r="B32" s="21">
@@ -6434,8 +6326,8 @@
       <c r="K32" s="24"/>
       <c r="L32" s="24"/>
     </row>
-    <row r="33" spans="1:12" ht="34.75">
-      <c r="A33" s="64"/>
+    <row r="33" spans="1:12" ht="36">
+      <c r="A33" s="71"/>
       <c r="B33" s="21">
         <v>44993</v>
       </c>
@@ -6458,8 +6350,8 @@
       <c r="K33" s="24"/>
       <c r="L33" s="24"/>
     </row>
-    <row r="34" spans="1:12" ht="23.15">
-      <c r="A34" s="64"/>
+    <row r="34" spans="1:12" ht="24">
+      <c r="A34" s="71"/>
       <c r="B34" s="21" t="s">
         <v>108</v>
       </c>
@@ -6484,8 +6376,8 @@
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
     </row>
-    <row r="35" spans="1:12" ht="23.15">
-      <c r="A35" s="64"/>
+    <row r="35" spans="1:12" ht="24">
+      <c r="A35" s="71"/>
       <c r="B35" s="21">
         <v>44995</v>
       </c>
@@ -6510,8 +6402,8 @@
       <c r="K35" s="24"/>
       <c r="L35" s="24"/>
     </row>
-    <row r="36" spans="1:12" ht="34.75">
-      <c r="A36" s="64"/>
+    <row r="36" spans="1:12" ht="36">
+      <c r="A36" s="71"/>
       <c r="B36" s="21">
         <v>44996</v>
       </c>
@@ -6534,8 +6426,8 @@
       <c r="K36" s="24"/>
       <c r="L36" s="24"/>
     </row>
-    <row r="37" spans="1:12" ht="115.75">
-      <c r="A37" s="64"/>
+    <row r="37" spans="1:12" ht="120">
+      <c r="A37" s="71"/>
       <c r="B37" s="21">
         <v>44997</v>
       </c>
@@ -6558,8 +6450,8 @@
       <c r="K37" s="24"/>
       <c r="L37" s="24"/>
     </row>
-    <row r="38" spans="1:12" ht="23.15">
-      <c r="A38" s="64"/>
+    <row r="38" spans="1:12" ht="24">
+      <c r="A38" s="71"/>
       <c r="B38" s="21">
         <v>44998</v>
       </c>
@@ -6580,8 +6472,8 @@
       <c r="K38" s="24"/>
       <c r="L38" s="24"/>
     </row>
-    <row r="39" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A39" s="63" t="s">
+    <row r="39" spans="1:12" ht="50" customHeight="1">
+      <c r="A39" s="70" t="s">
         <v>123</v>
       </c>
       <c r="B39" s="21">
@@ -6609,7 +6501,7 @@
       <c r="L39" s="24"/>
     </row>
     <row r="40" spans="1:12" ht="33" customHeight="1">
-      <c r="A40" s="64"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="21">
         <v>45000</v>
       </c>
@@ -6635,7 +6527,7 @@
       <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:12" ht="33" customHeight="1">
-      <c r="A41" s="64"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="21">
         <v>45001</v>
       </c>
@@ -6661,7 +6553,7 @@
       <c r="L41" s="24"/>
     </row>
     <row r="42" spans="1:12" ht="67" customHeight="1">
-      <c r="A42" s="64"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="21">
         <v>45002</v>
       </c>
@@ -6687,7 +6579,7 @@
       <c r="L42" s="24"/>
     </row>
     <row r="43" spans="1:12" ht="67" customHeight="1">
-      <c r="A43" s="64"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="21">
         <v>45003</v>
       </c>
@@ -6713,7 +6605,7 @@
       <c r="L43" s="24"/>
     </row>
     <row r="44" spans="1:12" ht="151" customHeight="1">
-      <c r="A44" s="64"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="21">
         <v>45004</v>
       </c>
@@ -6739,7 +6631,7 @@
       <c r="L44" s="24"/>
     </row>
     <row r="45" spans="1:12" ht="151" customHeight="1">
-      <c r="A45" s="64"/>
+      <c r="A45" s="71"/>
       <c r="B45" s="21">
         <v>45005</v>
       </c>
@@ -6765,7 +6657,7 @@
       <c r="L45" s="24"/>
     </row>
     <row r="46" spans="1:12" ht="33" customHeight="1">
-      <c r="A46" s="63" t="s">
+      <c r="A46" s="70" t="s">
         <v>153</v>
       </c>
       <c r="B46" s="21">
@@ -6791,7 +6683,7 @@
       <c r="L46" s="24"/>
     </row>
     <row r="47" spans="1:12" ht="33" customHeight="1">
-      <c r="A47" s="64"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="21">
         <v>45008</v>
       </c>
@@ -6814,8 +6706,8 @@
       <c r="K47" s="24"/>
       <c r="L47" s="24"/>
     </row>
-    <row r="48" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A48" s="64"/>
+    <row r="48" spans="1:12" ht="50" customHeight="1">
+      <c r="A48" s="71"/>
       <c r="B48" s="21">
         <v>45010</v>
       </c>
@@ -6841,7 +6733,7 @@
       <c r="L48" s="24"/>
     </row>
     <row r="49" spans="1:12" ht="55" customHeight="1">
-      <c r="A49" s="64"/>
+      <c r="A49" s="71"/>
       <c r="B49" s="21">
         <v>45011</v>
       </c>
@@ -6868,8 +6760,8 @@
       <c r="K49" s="24"/>
       <c r="L49" s="24"/>
     </row>
-    <row r="50" spans="1:12" ht="46.3">
-      <c r="A50" s="64"/>
+    <row r="50" spans="1:12" ht="48">
+      <c r="A50" s="71"/>
       <c r="B50" s="21">
         <v>45012</v>
       </c>
@@ -6895,7 +6787,7 @@
       <c r="L50" s="24"/>
     </row>
     <row r="51" spans="1:12" ht="67" customHeight="1">
-      <c r="A51" s="63" t="s">
+      <c r="A51" s="70" t="s">
         <v>169</v>
       </c>
       <c r="B51" s="21">
@@ -6920,8 +6812,8 @@
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
     </row>
-    <row r="52" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A52" s="64"/>
+    <row r="52" spans="1:12" ht="50" customHeight="1">
+      <c r="A52" s="71"/>
       <c r="B52" s="21">
         <v>45014</v>
       </c>
@@ -6948,8 +6840,8 @@
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
     </row>
-    <row r="53" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A53" s="64"/>
+    <row r="53" spans="1:12" ht="50" customHeight="1">
+      <c r="A53" s="71"/>
       <c r="B53" s="21">
         <v>45015</v>
       </c>
@@ -6976,8 +6868,8 @@
       <c r="K53" s="24"/>
       <c r="L53" s="24"/>
     </row>
-    <row r="54" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A54" s="64"/>
+    <row r="54" spans="1:12" ht="50" customHeight="1">
+      <c r="A54" s="71"/>
       <c r="B54" s="21">
         <v>45016</v>
       </c>
@@ -7001,7 +6893,7 @@
       <c r="L54" s="24"/>
     </row>
     <row r="55" spans="1:12" ht="33" customHeight="1">
-      <c r="A55" s="64"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="21">
         <v>45017</v>
       </c>
@@ -7026,8 +6918,8 @@
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
     </row>
-    <row r="56" spans="1:12" ht="134.05000000000001" customHeight="1">
-      <c r="A56" s="64"/>
+    <row r="56" spans="1:12" ht="134" customHeight="1">
+      <c r="A56" s="71"/>
       <c r="B56" s="21">
         <v>45018</v>
       </c>
@@ -7054,8 +6946,8 @@
       <c r="K56" s="24"/>
       <c r="L56" s="24"/>
     </row>
-    <row r="57" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A57" s="64"/>
+    <row r="57" spans="1:12" ht="50" customHeight="1">
+      <c r="A57" s="71"/>
       <c r="B57" s="21">
         <v>45019</v>
       </c>
@@ -7081,7 +6973,7 @@
       <c r="L57" s="24"/>
     </row>
     <row r="58" spans="1:12" ht="84" customHeight="1">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="70" t="s">
         <v>193</v>
       </c>
       <c r="B58" s="21">
@@ -7107,7 +6999,7 @@
       <c r="L58" s="24"/>
     </row>
     <row r="59" spans="1:12" ht="33" customHeight="1">
-      <c r="A59" s="64"/>
+      <c r="A59" s="71"/>
       <c r="B59" s="21">
         <v>45021</v>
       </c>
@@ -7135,7 +7027,7 @@
       <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:12" ht="33" customHeight="1">
-      <c r="A60" s="64"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="21">
         <v>45022</v>
       </c>
@@ -7156,8 +7048,8 @@
       <c r="K60" s="24"/>
       <c r="L60" s="24"/>
     </row>
-    <row r="61" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A61" s="64"/>
+    <row r="61" spans="1:12" ht="50" customHeight="1">
+      <c r="A61" s="71"/>
       <c r="B61" s="21">
         <v>45023</v>
       </c>
@@ -7184,8 +7076,8 @@
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
     </row>
-    <row r="62" spans="1:12" ht="46.3">
-      <c r="A62" s="64"/>
+    <row r="62" spans="1:12" ht="48">
+      <c r="A62" s="71"/>
       <c r="B62" s="21">
         <v>45025</v>
       </c>
@@ -7210,8 +7102,8 @@
       <c r="K62" s="24"/>
       <c r="L62" s="24"/>
     </row>
-    <row r="63" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A63" s="64"/>
+    <row r="63" spans="1:12" ht="50" customHeight="1">
+      <c r="A63" s="71"/>
       <c r="B63" s="21">
         <v>45026</v>
       </c>
@@ -7236,8 +7128,8 @@
       <c r="K63" s="24"/>
       <c r="L63" s="24"/>
     </row>
-    <row r="64" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A64" s="63" t="s">
+    <row r="64" spans="1:12" ht="50" customHeight="1">
+      <c r="A64" s="70" t="s">
         <v>215</v>
       </c>
       <c r="B64" s="21">
@@ -7263,7 +7155,7 @@
       <c r="L64" s="24"/>
     </row>
     <row r="65" spans="1:12" ht="33" customHeight="1">
-      <c r="A65" s="64"/>
+      <c r="A65" s="71"/>
       <c r="B65" s="21">
         <v>45028</v>
       </c>
@@ -7287,7 +7179,7 @@
       <c r="L65" s="24"/>
     </row>
     <row r="66" spans="1:12" ht="33" customHeight="1">
-      <c r="A66" s="64"/>
+      <c r="A66" s="71"/>
       <c r="B66" s="21">
         <v>45029</v>
       </c>
@@ -7311,7 +7203,7 @@
       <c r="L66" s="24"/>
     </row>
     <row r="67" spans="1:12" ht="84" customHeight="1">
-      <c r="A67" s="64"/>
+      <c r="A67" s="71"/>
       <c r="B67" s="21">
         <v>45030</v>
       </c>
@@ -7336,8 +7228,8 @@
       <c r="K67" s="24"/>
       <c r="L67" s="24"/>
     </row>
-    <row r="68" spans="1:12" ht="134.05000000000001" customHeight="1">
-      <c r="A68" s="64"/>
+    <row r="68" spans="1:12" ht="134" customHeight="1">
+      <c r="A68" s="71"/>
       <c r="B68" s="21">
         <v>45031</v>
       </c>
@@ -7363,7 +7255,7 @@
       <c r="L68" s="24"/>
     </row>
     <row r="69" spans="1:12" ht="67" customHeight="1">
-      <c r="A69" s="64"/>
+      <c r="A69" s="71"/>
       <c r="B69" s="21">
         <v>45032</v>
       </c>
@@ -7390,8 +7282,8 @@
       <c r="K69" s="24"/>
       <c r="L69" s="24"/>
     </row>
-    <row r="70" spans="1:12" ht="57.9">
-      <c r="A70" s="64"/>
+    <row r="70" spans="1:12" ht="60">
+      <c r="A70" s="71"/>
       <c r="B70" s="21">
         <v>45033</v>
       </c>
@@ -7418,8 +7310,8 @@
       <c r="K70" s="24"/>
       <c r="L70" s="24"/>
     </row>
-    <row r="71" spans="1:12" ht="134.05000000000001" customHeight="1">
-      <c r="A71" s="63" t="s">
+    <row r="71" spans="1:12" ht="134" customHeight="1">
+      <c r="A71" s="70" t="s">
         <v>237</v>
       </c>
       <c r="B71" s="21">
@@ -7448,8 +7340,8 @@
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
     </row>
-    <row r="72" spans="1:12" ht="12.45">
-      <c r="A72" s="64"/>
+    <row r="72" spans="1:12">
+      <c r="A72" s="71"/>
       <c r="B72" s="21">
         <v>45037</v>
       </c>
@@ -7469,7 +7361,7 @@
       <c r="L72" s="24"/>
     </row>
     <row r="73" spans="1:12" ht="67" customHeight="1">
-      <c r="A73" s="64"/>
+      <c r="A73" s="71"/>
       <c r="B73" s="21">
         <v>45038</v>
       </c>
@@ -7492,8 +7384,8 @@
       <c r="K73" s="24"/>
       <c r="L73" s="24"/>
     </row>
-    <row r="74" spans="1:12" ht="12.45">
-      <c r="A74" s="64"/>
+    <row r="74" spans="1:12">
+      <c r="A74" s="71"/>
       <c r="B74" s="21">
         <v>45039</v>
       </c>
@@ -7515,7 +7407,7 @@
       <c r="L74" s="24"/>
     </row>
     <row r="75" spans="1:12" ht="252" customHeight="1">
-      <c r="A75" s="64"/>
+      <c r="A75" s="71"/>
       <c r="B75" s="21">
         <v>45040</v>
       </c>
@@ -7541,7 +7433,7 @@
       <c r="L75" s="24"/>
     </row>
     <row r="76" spans="1:12" ht="33" customHeight="1">
-      <c r="A76" s="63" t="s">
+      <c r="A76" s="70" t="s">
         <v>250</v>
       </c>
       <c r="B76" s="21">
@@ -7569,7 +7461,7 @@
       <c r="L76" s="24"/>
     </row>
     <row r="77" spans="1:12" ht="117" customHeight="1">
-      <c r="A77" s="64"/>
+      <c r="A77" s="71"/>
       <c r="B77" s="21">
         <v>45042</v>
       </c>
@@ -7597,7 +7489,7 @@
       <c r="L77" s="24"/>
     </row>
     <row r="78" spans="1:12" ht="67" customHeight="1">
-      <c r="A78" s="64"/>
+      <c r="A78" s="71"/>
       <c r="B78" s="21">
         <v>45043</v>
       </c>
@@ -7623,7 +7515,7 @@
       <c r="L78" s="24"/>
     </row>
     <row r="79" spans="1:12" ht="33" customHeight="1">
-      <c r="A79" s="64"/>
+      <c r="A79" s="71"/>
       <c r="B79" s="21">
         <v>45044</v>
       </c>
@@ -7647,7 +7539,7 @@
       <c r="L79" s="24"/>
     </row>
     <row r="80" spans="1:12" ht="37" customHeight="1">
-      <c r="A80" s="64"/>
+      <c r="A80" s="71"/>
       <c r="B80" s="21">
         <v>45045</v>
       </c>
@@ -7672,8 +7564,8 @@
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
     </row>
-    <row r="81" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A81" s="64"/>
+    <row r="81" spans="1:12" ht="50" customHeight="1">
+      <c r="A81" s="71"/>
       <c r="B81" s="21">
         <v>45047</v>
       </c>
@@ -7697,7 +7589,7 @@
       <c r="L81" s="24"/>
     </row>
     <row r="82" spans="1:12" ht="33" customHeight="1">
-      <c r="A82" s="63" t="s">
+      <c r="A82" s="70" t="s">
         <v>272</v>
       </c>
       <c r="B82" s="21">
@@ -7724,8 +7616,8 @@
       <c r="K82" s="24"/>
       <c r="L82" s="24"/>
     </row>
-    <row r="83" spans="1:12" ht="56.05" customHeight="1">
-      <c r="A83" s="64"/>
+    <row r="83" spans="1:12" ht="56" customHeight="1">
+      <c r="A83" s="71"/>
       <c r="B83" s="21">
         <v>45050</v>
       </c>
@@ -7753,7 +7645,7 @@
       <c r="L83" s="24"/>
     </row>
     <row r="84" spans="1:12" ht="33" customHeight="1">
-      <c r="A84" s="64"/>
+      <c r="A84" s="71"/>
       <c r="B84" s="21">
         <v>45051</v>
       </c>
@@ -7777,7 +7669,7 @@
       <c r="L84" s="24"/>
     </row>
     <row r="85" spans="1:12" ht="100" customHeight="1">
-      <c r="A85" s="64"/>
+      <c r="A85" s="71"/>
       <c r="B85" s="21">
         <v>45052</v>
       </c>
@@ -7802,8 +7694,8 @@
       <c r="K85" s="24"/>
       <c r="L85" s="24"/>
     </row>
-    <row r="86" spans="1:12" ht="98.05" customHeight="1">
-      <c r="A86" s="64"/>
+    <row r="86" spans="1:12" ht="98" customHeight="1">
+      <c r="A86" s="71"/>
       <c r="B86" s="21">
         <v>45053</v>
       </c>
@@ -7830,8 +7722,8 @@
       <c r="K86" s="24"/>
       <c r="L86" s="24"/>
     </row>
-    <row r="87" spans="1:12" ht="24.9">
-      <c r="A87" s="64"/>
+    <row r="87" spans="1:12" ht="26">
+      <c r="A87" s="71"/>
       <c r="B87" s="21">
         <v>45054</v>
       </c>
@@ -7857,7 +7749,7 @@
       <c r="L87" s="24"/>
     </row>
     <row r="88" spans="1:12" ht="184" customHeight="1">
-      <c r="A88" s="63" t="s">
+      <c r="A88" s="70" t="s">
         <v>294</v>
       </c>
       <c r="B88" s="21">
@@ -7885,7 +7777,7 @@
       <c r="L88" s="24"/>
     </row>
     <row r="89" spans="1:12" ht="168" customHeight="1">
-      <c r="A89" s="64"/>
+      <c r="A89" s="71"/>
       <c r="B89" s="21">
         <v>45056</v>
       </c>
@@ -7911,7 +7803,7 @@
       <c r="L89" s="24"/>
     </row>
     <row r="90" spans="1:12" ht="67" customHeight="1">
-      <c r="A90" s="64"/>
+      <c r="A90" s="71"/>
       <c r="B90" s="21">
         <v>45057</v>
       </c>
@@ -7939,7 +7831,7 @@
       <c r="L90" s="24"/>
     </row>
     <row r="91" spans="1:12" ht="33" customHeight="1">
-      <c r="A91" s="64"/>
+      <c r="A91" s="71"/>
       <c r="B91" s="21">
         <v>45058</v>
       </c>
@@ -7962,8 +7854,8 @@
       <c r="K91" s="24"/>
       <c r="L91" s="24"/>
     </row>
-    <row r="92" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A92" s="64"/>
+    <row r="92" spans="1:12" ht="50" customHeight="1">
+      <c r="A92" s="71"/>
       <c r="B92" s="21">
         <v>45059</v>
       </c>
@@ -7989,7 +7881,7 @@
       <c r="L92" s="24"/>
     </row>
     <row r="93" spans="1:12" ht="84" customHeight="1">
-      <c r="A93" s="64"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="21">
         <v>45060</v>
       </c>
@@ -8012,8 +7904,8 @@
       <c r="K93" s="24"/>
       <c r="L93" s="24"/>
     </row>
-    <row r="94" spans="1:12" ht="89.05" customHeight="1">
-      <c r="A94" s="64"/>
+    <row r="94" spans="1:12" ht="89" customHeight="1">
+      <c r="A94" s="71"/>
       <c r="B94" s="21">
         <v>45061</v>
       </c>
@@ -8036,8 +7928,8 @@
       <c r="K94" s="24"/>
       <c r="L94" s="24"/>
     </row>
-    <row r="95" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A95" s="63" t="s">
+    <row r="95" spans="1:12" ht="50" customHeight="1">
+      <c r="A95" s="70" t="s">
         <v>316</v>
       </c>
       <c r="B95" s="21">
@@ -8063,7 +7955,7 @@
       <c r="L95" s="24"/>
     </row>
     <row r="96" spans="1:12" ht="100" customHeight="1">
-      <c r="A96" s="64"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="21">
         <v>45063</v>
       </c>
@@ -8088,8 +7980,8 @@
       <c r="K96" s="24"/>
       <c r="L96" s="24"/>
     </row>
-    <row r="97" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A97" s="64"/>
+    <row r="97" spans="1:12" ht="50" customHeight="1">
+      <c r="A97" s="71"/>
       <c r="B97" s="21">
         <v>45064</v>
       </c>
@@ -8113,7 +8005,7 @@
       <c r="L97" s="24"/>
     </row>
     <row r="98" spans="1:12" ht="84" customHeight="1">
-      <c r="A98" s="64"/>
+      <c r="A98" s="71"/>
       <c r="B98" s="21">
         <v>45065</v>
       </c>
@@ -8136,8 +8028,8 @@
       <c r="K98" s="24"/>
       <c r="L98" s="24"/>
     </row>
-    <row r="99" spans="1:12" ht="56.05" customHeight="1">
-      <c r="A99" s="64"/>
+    <row r="99" spans="1:12" ht="56" customHeight="1">
+      <c r="A99" s="71"/>
       <c r="B99" s="21">
         <v>45066</v>
       </c>
@@ -8162,8 +8054,8 @@
       <c r="K99" s="24"/>
       <c r="L99" s="24"/>
     </row>
-    <row r="100" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A100" s="64"/>
+    <row r="100" spans="1:12" ht="50" customHeight="1">
+      <c r="A100" s="71"/>
       <c r="B100" s="21">
         <v>45067</v>
       </c>
@@ -8186,8 +8078,8 @@
       <c r="K100" s="24"/>
       <c r="L100" s="24"/>
     </row>
-    <row r="101" spans="1:12" ht="27.45">
-      <c r="A101" s="64"/>
+    <row r="101" spans="1:12" ht="29">
+      <c r="A101" s="71"/>
       <c r="B101" s="21">
         <v>45068</v>
       </c>
@@ -8213,7 +8105,7 @@
       <c r="L101" s="24"/>
     </row>
     <row r="102" spans="1:12" ht="33" customHeight="1">
-      <c r="A102" s="63" t="s">
+      <c r="A102" s="70" t="s">
         <v>334</v>
       </c>
       <c r="B102" s="21">
@@ -8238,8 +8130,8 @@
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
     </row>
-    <row r="103" spans="1:12" ht="12.45">
-      <c r="A103" s="64"/>
+    <row r="103" spans="1:12">
+      <c r="A103" s="71"/>
       <c r="B103" s="21">
         <v>45071</v>
       </c>
@@ -8249,7 +8141,7 @@
       <c r="D103" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="E103" s="65" t="s">
+      <c r="E103" s="72" t="s">
         <v>338</v>
       </c>
       <c r="F103" s="22"/>
@@ -8260,8 +8152,8 @@
       <c r="K103" s="24"/>
       <c r="L103" s="24"/>
     </row>
-    <row r="104" spans="1:12" ht="12.45">
-      <c r="A104" s="64"/>
+    <row r="104" spans="1:12">
+      <c r="A104" s="71"/>
       <c r="B104" s="21">
         <v>45072</v>
       </c>
@@ -8271,7 +8163,7 @@
       <c r="D104" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E104" s="66"/>
+      <c r="E104" s="73"/>
       <c r="F104" s="22"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
@@ -8280,8 +8172,8 @@
       <c r="K104" s="24"/>
       <c r="L104" s="24"/>
     </row>
-    <row r="105" spans="1:12" ht="86.05" customHeight="1">
-      <c r="A105" s="64"/>
+    <row r="105" spans="1:12" ht="86" customHeight="1">
+      <c r="A105" s="71"/>
       <c r="B105" s="21">
         <v>45073</v>
       </c>
@@ -8304,8 +8196,8 @@
       <c r="K105" s="24"/>
       <c r="L105" s="24"/>
     </row>
-    <row r="106" spans="1:12" ht="68.05" customHeight="1">
-      <c r="A106" s="64"/>
+    <row r="106" spans="1:12" ht="68" customHeight="1">
+      <c r="A106" s="71"/>
       <c r="B106" s="21">
         <v>45074</v>
       </c>
@@ -8329,7 +8221,7 @@
       <c r="L106" s="24"/>
     </row>
     <row r="107" spans="1:12" ht="33" customHeight="1">
-      <c r="A107" s="63" t="s">
+      <c r="A107" s="70" t="s">
         <v>344</v>
       </c>
       <c r="B107" s="21">
@@ -8354,8 +8246,8 @@
       <c r="K107" s="24"/>
       <c r="L107" s="24"/>
     </row>
-    <row r="108" spans="1:12" ht="12.45">
-      <c r="A108" s="64"/>
+    <row r="108" spans="1:12">
+      <c r="A108" s="71"/>
       <c r="B108" s="21">
         <v>45077</v>
       </c>
@@ -8377,7 +8269,7 @@
       <c r="L108" s="24"/>
     </row>
     <row r="109" spans="1:12" ht="67" customHeight="1">
-      <c r="A109" s="64"/>
+      <c r="A109" s="71"/>
       <c r="B109" s="21">
         <v>45078</v>
       </c>
@@ -8401,7 +8293,7 @@
       <c r="L109" s="24"/>
     </row>
     <row r="110" spans="1:12" ht="205" customHeight="1">
-      <c r="A110" s="64"/>
+      <c r="A110" s="71"/>
       <c r="B110" s="21">
         <v>45079</v>
       </c>
@@ -8424,14 +8316,14 @@
       <c r="K110" s="24"/>
       <c r="L110" s="24"/>
     </row>
-    <row r="111" spans="1:12" ht="12.45">
-      <c r="A111" s="63" t="s">
+    <row r="111" spans="1:12">
+      <c r="A111" s="70" t="s">
         <v>354</v>
       </c>
-      <c r="B111" s="67" t="s">
+      <c r="B111" s="74" t="s">
         <v>355</v>
       </c>
-      <c r="C111" s="62"/>
+      <c r="C111" s="66"/>
       <c r="D111" s="21"/>
       <c r="E111" s="22"/>
       <c r="F111" s="22"/>
@@ -8442,10 +8334,10 @@
       <c r="K111" s="24"/>
       <c r="L111" s="24"/>
     </row>
-    <row r="112" spans="1:12" ht="12.45">
-      <c r="A112" s="64"/>
-      <c r="B112" s="62"/>
-      <c r="C112" s="62"/>
+    <row r="112" spans="1:12">
+      <c r="A112" s="71"/>
+      <c r="B112" s="66"/>
+      <c r="C112" s="66"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="22"/>
@@ -8456,14 +8348,14 @@
       <c r="K112" s="24"/>
       <c r="L112" s="24"/>
     </row>
-    <row r="113" spans="1:12" ht="12.45">
-      <c r="A113" s="63" t="s">
+    <row r="113" spans="1:12">
+      <c r="A113" s="70" t="s">
         <v>356</v>
       </c>
-      <c r="B113" s="67" t="s">
+      <c r="B113" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="C113" s="62"/>
+      <c r="C113" s="66"/>
       <c r="D113" s="21"/>
       <c r="E113" s="22"/>
       <c r="F113" s="22"/>
@@ -8474,10 +8366,10 @@
       <c r="K113" s="24"/>
       <c r="L113" s="24"/>
     </row>
-    <row r="114" spans="1:12" ht="12.45">
-      <c r="A114" s="64"/>
-      <c r="B114" s="62"/>
-      <c r="C114" s="62"/>
+    <row r="114" spans="1:12">
+      <c r="A114" s="71"/>
+      <c r="B114" s="66"/>
+      <c r="C114" s="66"/>
       <c r="D114" s="21"/>
       <c r="E114" s="22"/>
       <c r="F114" s="22"/>
@@ -8488,14 +8380,14 @@
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
     </row>
-    <row r="115" spans="1:12" ht="12.45">
-      <c r="A115" s="63" t="s">
+    <row r="115" spans="1:12">
+      <c r="A115" s="70" t="s">
         <v>358</v>
       </c>
-      <c r="B115" s="67" t="s">
+      <c r="B115" s="74" t="s">
         <v>359</v>
       </c>
-      <c r="C115" s="62"/>
+      <c r="C115" s="66"/>
       <c r="D115" s="21"/>
       <c r="E115" s="22"/>
       <c r="F115" s="22"/>
@@ -8506,10 +8398,10 @@
       <c r="K115" s="24"/>
       <c r="L115" s="24"/>
     </row>
-    <row r="116" spans="1:12" ht="12.45">
-      <c r="A116" s="64"/>
-      <c r="B116" s="62"/>
-      <c r="C116" s="62"/>
+    <row r="116" spans="1:12">
+      <c r="A116" s="71"/>
+      <c r="B116" s="66"/>
+      <c r="C116" s="66"/>
       <c r="D116" s="21"/>
       <c r="E116" s="22"/>
       <c r="F116" s="22"/>
@@ -8521,7 +8413,7 @@
       <c r="L116" s="24"/>
     </row>
     <row r="117" spans="1:12" ht="37" customHeight="1">
-      <c r="A117" s="63" t="s">
+      <c r="A117" s="70" t="s">
         <v>360</v>
       </c>
       <c r="B117" s="21">
@@ -8546,8 +8438,8 @@
       <c r="K117" s="24"/>
       <c r="L117" s="24"/>
     </row>
-    <row r="118" spans="1:12" ht="302.05" customHeight="1">
-      <c r="A118" s="64"/>
+    <row r="118" spans="1:12" ht="302" customHeight="1">
+      <c r="A118" s="71"/>
       <c r="B118" s="21">
         <v>45105</v>
       </c>
@@ -8575,7 +8467,7 @@
       <c r="L118" s="24"/>
     </row>
     <row r="119" spans="1:12" ht="201" customHeight="1">
-      <c r="A119" s="64"/>
+      <c r="A119" s="71"/>
       <c r="B119" s="21">
         <v>45106</v>
       </c>
@@ -8603,7 +8495,7 @@
       <c r="L119" s="24"/>
     </row>
     <row r="120" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A120" s="64"/>
+      <c r="A120" s="71"/>
       <c r="B120" s="21">
         <v>45107</v>
       </c>
@@ -8631,7 +8523,7 @@
       <c r="L120" s="24"/>
     </row>
     <row r="121" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A121" s="64"/>
+      <c r="A121" s="71"/>
       <c r="B121" s="21">
         <v>45108</v>
       </c>
@@ -8659,7 +8551,7 @@
       <c r="L121" s="24"/>
     </row>
     <row r="122" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A122" s="64"/>
+      <c r="A122" s="71"/>
       <c r="B122" s="21">
         <v>45109</v>
       </c>
@@ -8685,7 +8577,7 @@
       <c r="L122" s="24"/>
     </row>
     <row r="123" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A123" s="64"/>
+      <c r="A123" s="71"/>
       <c r="B123" s="21">
         <v>45110</v>
       </c>
@@ -8711,7 +8603,7 @@
       <c r="L123" s="24"/>
     </row>
     <row r="124" spans="1:12" ht="67" customHeight="1">
-      <c r="A124" s="63" t="s">
+      <c r="A124" s="70" t="s">
         <v>381</v>
       </c>
       <c r="B124" s="21">
@@ -8738,8 +8630,8 @@
       <c r="K124" s="24"/>
       <c r="L124" s="24"/>
     </row>
-    <row r="125" spans="1:12" ht="386.05" customHeight="1">
-      <c r="A125" s="64"/>
+    <row r="125" spans="1:12" ht="386" customHeight="1">
+      <c r="A125" s="71"/>
       <c r="B125" s="21">
         <v>45112</v>
       </c>
@@ -8767,7 +8659,7 @@
       <c r="L125" s="24"/>
     </row>
     <row r="126" spans="1:12" ht="100" customHeight="1">
-      <c r="A126" s="64"/>
+      <c r="A126" s="71"/>
       <c r="B126" s="21">
         <v>45113</v>
       </c>
@@ -8794,8 +8686,8 @@
       <c r="K126" s="24"/>
       <c r="L126" s="24"/>
     </row>
-    <row r="127" spans="1:12" ht="302.05" customHeight="1">
-      <c r="A127" s="64"/>
+    <row r="127" spans="1:12" ht="302" customHeight="1">
+      <c r="A127" s="71"/>
       <c r="B127" s="21">
         <v>45114</v>
       </c>
@@ -8821,7 +8713,7 @@
       <c r="L127" s="24"/>
     </row>
     <row r="128" spans="1:12" ht="100" customHeight="1">
-      <c r="A128" s="64"/>
+      <c r="A128" s="71"/>
       <c r="B128" s="21">
         <v>45115</v>
       </c>
@@ -8849,7 +8741,7 @@
       <c r="L128" s="24"/>
     </row>
     <row r="129" spans="1:12" ht="33" customHeight="1">
-      <c r="A129" s="64"/>
+      <c r="A129" s="71"/>
       <c r="B129" s="21">
         <v>45116</v>
       </c>
@@ -8875,7 +8767,7 @@
       <c r="L129" s="24"/>
     </row>
     <row r="130" spans="1:12" ht="100" customHeight="1">
-      <c r="A130" s="64"/>
+      <c r="A130" s="71"/>
       <c r="B130" s="21">
         <v>45117</v>
       </c>
@@ -8901,7 +8793,7 @@
       <c r="L130" s="24"/>
     </row>
     <row r="131" spans="1:12" ht="100" customHeight="1">
-      <c r="A131" s="63" t="s">
+      <c r="A131" s="70" t="s">
         <v>409</v>
       </c>
       <c r="B131" s="21">
@@ -8928,8 +8820,8 @@
       <c r="K131" s="24"/>
       <c r="L131" s="24"/>
     </row>
-    <row r="132" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A132" s="64"/>
+    <row r="132" spans="1:12" ht="50" customHeight="1">
+      <c r="A132" s="71"/>
       <c r="B132" s="21">
         <v>45119</v>
       </c>
@@ -8957,7 +8849,7 @@
       <c r="L132" s="24"/>
     </row>
     <row r="133" spans="1:12" ht="168" customHeight="1">
-      <c r="A133" s="64"/>
+      <c r="A133" s="71"/>
       <c r="B133" s="21">
         <v>45120</v>
       </c>
@@ -8982,8 +8874,8 @@
       <c r="K133" s="24"/>
       <c r="L133" s="24"/>
     </row>
-    <row r="134" spans="1:12" ht="302.05" customHeight="1">
-      <c r="A134" s="64"/>
+    <row r="134" spans="1:12" ht="302" customHeight="1">
+      <c r="A134" s="71"/>
       <c r="B134" s="21">
         <v>45121</v>
       </c>
@@ -9009,7 +8901,7 @@
       <c r="L134" s="24"/>
     </row>
     <row r="135" spans="1:12" ht="168" customHeight="1">
-      <c r="A135" s="64"/>
+      <c r="A135" s="71"/>
       <c r="B135" s="21">
         <v>45122</v>
       </c>
@@ -9037,7 +8929,7 @@
       <c r="L135" s="24"/>
     </row>
     <row r="136" spans="1:12" ht="268" customHeight="1">
-      <c r="A136" s="64"/>
+      <c r="A136" s="71"/>
       <c r="B136" s="21">
         <v>45123</v>
       </c>
@@ -9062,8 +8954,8 @@
       <c r="K136" s="24"/>
       <c r="L136" s="24"/>
     </row>
-    <row r="137" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A137" s="64"/>
+    <row r="137" spans="1:12" ht="50" customHeight="1">
+      <c r="A137" s="71"/>
       <c r="B137" s="21">
         <v>45124</v>
       </c>
@@ -9087,7 +8979,7 @@
       <c r="L137" s="24"/>
     </row>
     <row r="138" spans="1:12" ht="336" customHeight="1">
-      <c r="A138" s="63" t="s">
+      <c r="A138" s="70" t="s">
         <v>430</v>
       </c>
       <c r="B138" s="21">
@@ -9115,7 +9007,7 @@
       <c r="L138" s="24"/>
     </row>
     <row r="139" spans="1:12" ht="235" customHeight="1">
-      <c r="A139" s="64"/>
+      <c r="A139" s="71"/>
       <c r="B139" s="21">
         <v>45126</v>
       </c>
@@ -9141,7 +9033,7 @@
       <c r="L139" s="24"/>
     </row>
     <row r="140" spans="1:12" ht="352" customHeight="1">
-      <c r="A140" s="64"/>
+      <c r="A140" s="71"/>
       <c r="B140" s="21">
         <v>45127</v>
       </c>
@@ -9167,7 +9059,7 @@
       <c r="L140" s="24"/>
     </row>
     <row r="141" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A141" s="64"/>
+      <c r="A141" s="71"/>
       <c r="B141" s="21">
         <v>45128</v>
       </c>
@@ -9193,7 +9085,7 @@
       <c r="L141" s="24"/>
     </row>
     <row r="142" spans="1:12" ht="252" customHeight="1">
-      <c r="A142" s="64"/>
+      <c r="A142" s="71"/>
       <c r="B142" s="21">
         <v>45129</v>
       </c>
@@ -9219,7 +9111,7 @@
       <c r="L142" s="24"/>
     </row>
     <row r="143" spans="1:12" ht="336" customHeight="1">
-      <c r="A143" s="64"/>
+      <c r="A143" s="71"/>
       <c r="B143" s="21">
         <v>45130</v>
       </c>
@@ -9245,7 +9137,7 @@
       <c r="L143" s="24"/>
     </row>
     <row r="144" spans="1:12" ht="235" customHeight="1">
-      <c r="A144" s="63" t="s">
+      <c r="A144" s="70" t="s">
         <v>448</v>
       </c>
       <c r="B144" s="21">
@@ -9273,7 +9165,7 @@
       <c r="L144" s="24"/>
     </row>
     <row r="145" spans="1:12" ht="67" customHeight="1">
-      <c r="A145" s="64"/>
+      <c r="A145" s="71"/>
       <c r="B145" s="21">
         <v>45132</v>
       </c>
@@ -9301,7 +9193,7 @@
       <c r="L145" s="24"/>
     </row>
     <row r="146" spans="1:12" ht="409.6" customHeight="1">
-      <c r="A146" s="64"/>
+      <c r="A146" s="71"/>
       <c r="B146" s="21">
         <v>45133</v>
       </c>
@@ -9327,7 +9219,7 @@
       <c r="L146" s="24"/>
     </row>
     <row r="147" spans="1:12" ht="336" customHeight="1">
-      <c r="A147" s="64"/>
+      <c r="A147" s="71"/>
       <c r="B147" s="21">
         <v>45134</v>
       </c>
@@ -9355,7 +9247,7 @@
       <c r="L147" s="24"/>
     </row>
     <row r="148" spans="1:12" ht="285" customHeight="1">
-      <c r="A148" s="64"/>
+      <c r="A148" s="71"/>
       <c r="B148" s="21">
         <v>45135</v>
       </c>
@@ -9382,8 +9274,8 @@
       <c r="K148" s="24"/>
       <c r="L148" s="24"/>
     </row>
-    <row r="149" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A149" s="64"/>
+    <row r="149" spans="1:12" ht="50" customHeight="1">
+      <c r="A149" s="71"/>
       <c r="B149" s="21">
         <v>45136</v>
       </c>
@@ -9411,7 +9303,7 @@
       <c r="L149" s="24"/>
     </row>
     <row r="150" spans="1:12" ht="336" customHeight="1">
-      <c r="A150" s="64"/>
+      <c r="A150" s="71"/>
       <c r="B150" s="21">
         <v>45137</v>
       </c>
@@ -9438,8 +9330,8 @@
       <c r="K150" s="24"/>
       <c r="L150" s="24"/>
     </row>
-    <row r="151" spans="1:12" ht="12.45">
-      <c r="A151" s="64"/>
+    <row r="151" spans="1:12">
+      <c r="A151" s="71"/>
       <c r="B151" s="21">
         <v>45138</v>
       </c>
@@ -9459,7 +9351,7 @@
       <c r="L151" s="24"/>
     </row>
     <row r="152" spans="1:12" ht="117" customHeight="1">
-      <c r="A152" s="63" t="s">
+      <c r="A152" s="70" t="s">
         <v>476</v>
       </c>
       <c r="B152" s="21">
@@ -9485,7 +9377,7 @@
       <c r="L152" s="24"/>
     </row>
     <row r="153" spans="1:12" ht="151" customHeight="1">
-      <c r="A153" s="64"/>
+      <c r="A153" s="71"/>
       <c r="B153" s="21">
         <v>45140</v>
       </c>
@@ -9510,8 +9402,8 @@
       <c r="K153" s="24"/>
       <c r="L153" s="24"/>
     </row>
-    <row r="154" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A154" s="64"/>
+    <row r="154" spans="1:12" ht="50" customHeight="1">
+      <c r="A154" s="71"/>
       <c r="B154" s="21">
         <v>45141</v>
       </c>
@@ -9533,7 +9425,7 @@
       <c r="L154" s="24"/>
     </row>
     <row r="155" spans="1:12" ht="33" customHeight="1">
-      <c r="A155" s="64"/>
+      <c r="A155" s="71"/>
       <c r="B155" s="21">
         <v>45142</v>
       </c>
@@ -9555,7 +9447,7 @@
       <c r="L155" s="24"/>
     </row>
     <row r="156" spans="1:12" ht="352" customHeight="1">
-      <c r="A156" s="64"/>
+      <c r="A156" s="71"/>
       <c r="B156" s="21">
         <v>45143</v>
       </c>
@@ -9581,7 +9473,7 @@
       <c r="L156" s="24"/>
     </row>
     <row r="157" spans="1:12" ht="336" customHeight="1">
-      <c r="A157" s="64"/>
+      <c r="A157" s="71"/>
       <c r="B157" s="21">
         <v>45144</v>
       </c>
@@ -9604,8 +9496,8 @@
       <c r="K157" s="24"/>
       <c r="L157" s="24"/>
     </row>
-    <row r="158" spans="1:12" ht="218.05" customHeight="1">
-      <c r="A158" s="64"/>
+    <row r="158" spans="1:12" ht="218" customHeight="1">
+      <c r="A158" s="71"/>
       <c r="B158" s="21">
         <v>45145</v>
       </c>
@@ -9630,8 +9522,8 @@
       <c r="K158" s="24"/>
       <c r="L158" s="24"/>
     </row>
-    <row r="159" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A159" s="63" t="s">
+    <row r="159" spans="1:12" ht="50" customHeight="1">
+      <c r="A159" s="70" t="s">
         <v>494</v>
       </c>
       <c r="B159" s="21">
@@ -9655,7 +9547,7 @@
       <c r="L159" s="24"/>
     </row>
     <row r="160" spans="1:12" ht="33" customHeight="1">
-      <c r="A160" s="64"/>
+      <c r="A160" s="71"/>
       <c r="B160" s="21">
         <v>45147</v>
       </c>
@@ -9679,7 +9571,7 @@
       <c r="L160" s="24"/>
     </row>
     <row r="161" spans="1:12" ht="33" customHeight="1">
-      <c r="A161" s="64"/>
+      <c r="A161" s="71"/>
       <c r="B161" s="21">
         <v>45148</v>
       </c>
@@ -9701,7 +9593,7 @@
       <c r="L161" s="24"/>
     </row>
     <row r="162" spans="1:12" ht="33" customHeight="1">
-      <c r="A162" s="64"/>
+      <c r="A162" s="71"/>
       <c r="B162" s="21">
         <v>45149</v>
       </c>
@@ -9723,7 +9615,7 @@
       <c r="L162" s="24"/>
     </row>
     <row r="163" spans="1:12" ht="100" customHeight="1">
-      <c r="A163" s="64"/>
+      <c r="A163" s="71"/>
       <c r="B163" s="21">
         <v>45150</v>
       </c>
@@ -9747,7 +9639,7 @@
       <c r="L163" s="24"/>
     </row>
     <row r="164" spans="1:12" ht="168" customHeight="1">
-      <c r="A164" s="64"/>
+      <c r="A164" s="71"/>
       <c r="B164" s="21">
         <v>45151</v>
       </c>
@@ -9770,8 +9662,8 @@
       <c r="K164" s="24"/>
       <c r="L164" s="24"/>
     </row>
-    <row r="165" spans="1:12" ht="12.45">
-      <c r="A165" s="64"/>
+    <row r="165" spans="1:12">
+      <c r="A165" s="71"/>
       <c r="B165" s="21">
         <v>45152</v>
       </c>
@@ -9793,7 +9685,7 @@
       <c r="L165" s="24"/>
     </row>
     <row r="166" spans="1:12" ht="117" customHeight="1">
-      <c r="A166" s="63" t="s">
+      <c r="A166" s="70" t="s">
         <v>511</v>
       </c>
       <c r="B166" s="21">
@@ -9818,8 +9710,8 @@
       <c r="K166" s="24"/>
       <c r="L166" s="24"/>
     </row>
-    <row r="167" spans="1:12" ht="12.45">
-      <c r="A167" s="64"/>
+    <row r="167" spans="1:12">
+      <c r="A167" s="71"/>
       <c r="B167" s="21">
         <v>45154</v>
       </c>
@@ -9829,7 +9721,7 @@
       <c r="D167" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="E167" s="68" t="s">
+      <c r="E167" s="75" t="s">
         <v>514</v>
       </c>
       <c r="F167" s="22"/>
@@ -9840,8 +9732,8 @@
       <c r="K167" s="24"/>
       <c r="L167" s="24"/>
     </row>
-    <row r="168" spans="1:12" ht="12.45">
-      <c r="A168" s="64"/>
+    <row r="168" spans="1:12">
+      <c r="A168" s="71"/>
       <c r="B168" s="21">
         <v>45155</v>
       </c>
@@ -9851,7 +9743,7 @@
       <c r="D168" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="E168" s="69"/>
+      <c r="E168" s="76"/>
       <c r="F168" s="22"/>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -9860,8 +9752,8 @@
       <c r="K168" s="24"/>
       <c r="L168" s="24"/>
     </row>
-    <row r="169" spans="1:12" ht="12.45">
-      <c r="A169" s="64"/>
+    <row r="169" spans="1:12">
+      <c r="A169" s="71"/>
       <c r="B169" s="21">
         <v>45156</v>
       </c>
@@ -9871,7 +9763,7 @@
       <c r="D169" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="E169" s="68" t="s">
+      <c r="E169" s="75" t="s">
         <v>517</v>
       </c>
       <c r="F169" s="22"/>
@@ -9882,8 +9774,8 @@
       <c r="K169" s="24"/>
       <c r="L169" s="24"/>
     </row>
-    <row r="170" spans="1:12" ht="12.45">
-      <c r="A170" s="64"/>
+    <row r="170" spans="1:12">
+      <c r="A170" s="71"/>
       <c r="B170" s="21">
         <v>45157</v>
       </c>
@@ -9893,7 +9785,7 @@
       <c r="D170" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="E170" s="69"/>
+      <c r="E170" s="76"/>
       <c r="F170" s="22"/>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -9903,7 +9795,7 @@
       <c r="L170" s="24"/>
     </row>
     <row r="171" spans="1:12" ht="37" customHeight="1">
-      <c r="A171" s="64"/>
+      <c r="A171" s="71"/>
       <c r="B171" s="21" t="s">
         <v>518</v>
       </c>
@@ -9913,7 +9805,7 @@
       <c r="D171" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="E171" s="68" t="s">
+      <c r="E171" s="75" t="s">
         <v>520</v>
       </c>
       <c r="F171" s="22"/>
@@ -9926,8 +9818,8 @@
       <c r="K171" s="24"/>
       <c r="L171" s="24"/>
     </row>
-    <row r="172" spans="1:12" ht="12.45">
-      <c r="A172" s="64"/>
+    <row r="172" spans="1:12">
+      <c r="A172" s="71"/>
       <c r="B172" s="21">
         <v>45159</v>
       </c>
@@ -9937,7 +9829,7 @@
       <c r="D172" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="E172" s="69"/>
+      <c r="E172" s="76"/>
       <c r="F172" s="22"/>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
@@ -9946,8 +9838,8 @@
       <c r="K172" s="24"/>
       <c r="L172" s="24"/>
     </row>
-    <row r="173" spans="1:12" ht="12.45">
-      <c r="A173" s="63" t="s">
+    <row r="173" spans="1:12">
+      <c r="A173" s="70" t="s">
         <v>523</v>
       </c>
       <c r="B173" s="21">
@@ -9971,7 +9863,7 @@
       <c r="L173" s="24"/>
     </row>
     <row r="174" spans="1:12" ht="100" customHeight="1">
-      <c r="A174" s="64"/>
+      <c r="A174" s="71"/>
       <c r="B174" s="21">
         <v>45161</v>
       </c>
@@ -9994,8 +9886,8 @@
       <c r="K174" s="24"/>
       <c r="L174" s="24"/>
     </row>
-    <row r="175" spans="1:12" ht="12.45">
-      <c r="A175" s="64"/>
+    <row r="175" spans="1:12">
+      <c r="A175" s="71"/>
       <c r="B175" s="21">
         <v>45162</v>
       </c>
@@ -10013,7 +9905,7 @@
       <c r="L175" s="24"/>
     </row>
     <row r="176" spans="1:12" ht="33" customHeight="1">
-      <c r="A176" s="64"/>
+      <c r="A176" s="71"/>
       <c r="B176" s="21">
         <v>45163</v>
       </c>
@@ -10038,18 +9930,18 @@
       <c r="K176" s="24"/>
       <c r="L176" s="24"/>
     </row>
-    <row r="177" spans="1:12" ht="12.45">
-      <c r="A177" s="64"/>
+    <row r="177" spans="1:12">
+      <c r="A177" s="71"/>
       <c r="B177" s="21">
         <v>45164</v>
       </c>
-      <c r="C177" s="67" t="s">
+      <c r="C177" s="74" t="s">
         <v>533</v>
       </c>
-      <c r="D177" s="67" t="s">
+      <c r="D177" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="E177" s="68" t="s">
+      <c r="E177" s="75" t="s">
         <v>534</v>
       </c>
       <c r="F177" s="22"/>
@@ -10060,14 +9952,14 @@
       <c r="K177" s="24"/>
       <c r="L177" s="24"/>
     </row>
-    <row r="178" spans="1:12" ht="12.45">
-      <c r="A178" s="64"/>
+    <row r="178" spans="1:12">
+      <c r="A178" s="71"/>
       <c r="B178" s="21">
         <v>45165</v>
       </c>
-      <c r="C178" s="62"/>
-      <c r="D178" s="62"/>
-      <c r="E178" s="69"/>
+      <c r="C178" s="66"/>
+      <c r="D178" s="66"/>
+      <c r="E178" s="76"/>
       <c r="F178" s="22"/>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
@@ -10076,8 +9968,8 @@
       <c r="K178" s="24"/>
       <c r="L178" s="24"/>
     </row>
-    <row r="179" spans="1:12" ht="12.45">
-      <c r="A179" s="64"/>
+    <row r="179" spans="1:12">
+      <c r="A179" s="71"/>
       <c r="B179" s="21">
         <v>45166</v>
       </c>
@@ -10094,14 +9986,14 @@
       <c r="K179" s="24"/>
       <c r="L179" s="24"/>
     </row>
-    <row r="180" spans="1:12" ht="12.45">
-      <c r="A180" s="63" t="s">
+    <row r="180" spans="1:12">
+      <c r="A180" s="70" t="s">
         <v>536</v>
       </c>
       <c r="B180" s="21">
         <v>45167</v>
       </c>
-      <c r="C180" s="67" t="s">
+      <c r="C180" s="74" t="s">
         <v>537</v>
       </c>
       <c r="D180" s="21"/>
@@ -10114,12 +10006,12 @@
       <c r="K180" s="24"/>
       <c r="L180" s="24"/>
     </row>
-    <row r="181" spans="1:12" ht="12.45">
-      <c r="A181" s="64"/>
+    <row r="181" spans="1:12">
+      <c r="A181" s="71"/>
       <c r="B181" s="21">
         <v>45168</v>
       </c>
-      <c r="C181" s="62"/>
+      <c r="C181" s="66"/>
       <c r="D181" s="21"/>
       <c r="E181" s="22"/>
       <c r="F181" s="22"/>
@@ -10130,12 +10022,12 @@
       <c r="K181" s="24"/>
       <c r="L181" s="24"/>
     </row>
-    <row r="182" spans="1:12" ht="12.45">
-      <c r="A182" s="64"/>
+    <row r="182" spans="1:12">
+      <c r="A182" s="71"/>
       <c r="B182" s="21">
         <v>45169</v>
       </c>
-      <c r="C182" s="62"/>
+      <c r="C182" s="66"/>
       <c r="D182" s="21"/>
       <c r="E182" s="22"/>
       <c r="F182" s="22"/>
@@ -10147,7 +10039,7 @@
       <c r="L182" s="24"/>
     </row>
     <row r="183" spans="1:12" ht="33" customHeight="1">
-      <c r="A183" s="64"/>
+      <c r="A183" s="71"/>
       <c r="B183" s="21">
         <v>45170</v>
       </c>
@@ -10170,12 +10062,12 @@
       <c r="K183" s="24"/>
       <c r="L183" s="24"/>
     </row>
-    <row r="184" spans="1:12" ht="12.45">
-      <c r="A184" s="64"/>
+    <row r="184" spans="1:12">
+      <c r="A184" s="71"/>
       <c r="B184" s="21">
         <v>45171</v>
       </c>
-      <c r="C184" s="67" t="s">
+      <c r="C184" s="74" t="s">
         <v>541</v>
       </c>
       <c r="D184" s="21" t="s">
@@ -10193,11 +10085,11 @@
       <c r="L184" s="24"/>
     </row>
     <row r="185" spans="1:12" ht="235" customHeight="1">
-      <c r="A185" s="64"/>
+      <c r="A185" s="71"/>
       <c r="B185" s="21">
         <v>45172</v>
       </c>
-      <c r="C185" s="62"/>
+      <c r="C185" s="66"/>
       <c r="D185" s="21" t="s">
         <v>171</v>
       </c>
@@ -10214,8 +10106,8 @@
       <c r="K185" s="24"/>
       <c r="L185" s="24"/>
     </row>
-    <row r="186" spans="1:12" ht="74.05" customHeight="1">
-      <c r="A186" s="64"/>
+    <row r="186" spans="1:12" ht="74" customHeight="1">
+      <c r="A186" s="71"/>
       <c r="B186" s="21">
         <v>45173</v>
       </c>
@@ -10238,8 +10130,8 @@
       <c r="K186" s="24"/>
       <c r="L186" s="24"/>
     </row>
-    <row r="187" spans="1:12" ht="12.45">
-      <c r="A187" s="63" t="s">
+    <row r="187" spans="1:12">
+      <c r="A187" s="70" t="s">
         <v>548</v>
       </c>
       <c r="B187" s="21">
@@ -10262,21 +10154,21 @@
       <c r="K187" s="24"/>
       <c r="L187" s="24"/>
     </row>
-    <row r="188" spans="1:12" ht="12.45">
-      <c r="A188" s="64"/>
+    <row r="188" spans="1:12">
+      <c r="A188" s="71"/>
       <c r="B188" s="21">
         <v>45175</v>
       </c>
-      <c r="C188" s="67" t="s">
+      <c r="C188" s="74" t="s">
         <v>551</v>
       </c>
-      <c r="D188" s="67" t="s">
+      <c r="D188" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="E188" s="68" t="s">
+      <c r="E188" s="75" t="s">
         <v>552</v>
       </c>
-      <c r="F188" s="68" t="s">
+      <c r="F188" s="75" t="s">
         <v>553</v>
       </c>
       <c r="G188" s="24"/>
@@ -10286,15 +10178,15 @@
       <c r="K188" s="24"/>
       <c r="L188" s="24"/>
     </row>
-    <row r="189" spans="1:12" ht="89.05" customHeight="1">
-      <c r="A189" s="64"/>
+    <row r="189" spans="1:12" ht="89" customHeight="1">
+      <c r="A189" s="71"/>
       <c r="B189" s="21">
         <v>45176</v>
       </c>
-      <c r="C189" s="62"/>
-      <c r="D189" s="62"/>
-      <c r="E189" s="69"/>
-      <c r="F189" s="69"/>
+      <c r="C189" s="66"/>
+      <c r="D189" s="66"/>
+      <c r="E189" s="76"/>
+      <c r="F189" s="76"/>
       <c r="G189" s="24"/>
       <c r="H189" s="24"/>
       <c r="I189" s="1"/>
@@ -10303,7 +10195,7 @@
       <c r="L189" s="24"/>
     </row>
     <row r="190" spans="1:12" ht="201" customHeight="1">
-      <c r="A190" s="64"/>
+      <c r="A190" s="71"/>
       <c r="B190" s="21">
         <v>45177</v>
       </c>
@@ -10329,7 +10221,7 @@
       <c r="L190" s="24"/>
     </row>
     <row r="191" spans="1:12" ht="100" customHeight="1">
-      <c r="A191" s="64"/>
+      <c r="A191" s="71"/>
       <c r="B191" s="21">
         <v>45178</v>
       </c>
@@ -10352,8 +10244,8 @@
       <c r="K191" s="24"/>
       <c r="L191" s="24"/>
     </row>
-    <row r="192" spans="1:12" ht="134.05000000000001" customHeight="1">
-      <c r="A192" s="64"/>
+    <row r="192" spans="1:12" ht="134" customHeight="1">
+      <c r="A192" s="71"/>
       <c r="B192" s="21">
         <v>45179</v>
       </c>
@@ -10379,7 +10271,7 @@
       <c r="L192" s="24"/>
     </row>
     <row r="193" spans="1:12" ht="117" customHeight="1">
-      <c r="A193" s="64"/>
+      <c r="A193" s="71"/>
       <c r="B193" s="21">
         <v>45180</v>
       </c>
@@ -10403,7 +10295,7 @@
       <c r="L193" s="24"/>
     </row>
     <row r="194" spans="1:12" ht="84" customHeight="1">
-      <c r="A194" s="63" t="s">
+      <c r="A194" s="70" t="s">
         <v>566</v>
       </c>
       <c r="B194" s="21">
@@ -10428,8 +10320,8 @@
       <c r="K194" s="24"/>
       <c r="L194" s="24"/>
     </row>
-    <row r="195" spans="1:12" ht="50.05" customHeight="1">
-      <c r="A195" s="64"/>
+    <row r="195" spans="1:12" ht="50" customHeight="1">
+      <c r="A195" s="71"/>
       <c r="B195" s="21">
         <v>45182</v>
       </c>
@@ -10450,8 +10342,8 @@
       <c r="K195" s="24"/>
       <c r="L195" s="24"/>
     </row>
-    <row r="196" spans="1:12" ht="12.45">
-      <c r="A196" s="64"/>
+    <row r="196" spans="1:12">
+      <c r="A196" s="71"/>
       <c r="B196" s="21">
         <v>45183</v>
       </c>
@@ -10471,7 +10363,7 @@
       <c r="L196" s="24"/>
     </row>
     <row r="197" spans="1:12" ht="100" customHeight="1">
-      <c r="A197" s="64"/>
+      <c r="A197" s="71"/>
       <c r="B197" s="21">
         <v>45184</v>
       </c>
@@ -10492,46 +10384,46 @@
       <c r="K197" s="24"/>
       <c r="L197" s="24"/>
     </row>
-    <row r="198" spans="1:12" ht="12.45">
-      <c r="A198" s="70" t="s">
+    <row r="198" spans="1:12">
+      <c r="A198" s="77" t="s">
         <v>474</v>
       </c>
-      <c r="B198" s="71" t="s">
+      <c r="B198" s="78" t="s">
         <v>574</v>
       </c>
-      <c r="C198" s="62"/>
-      <c r="D198" s="72"/>
-      <c r="E198" s="73"/>
-      <c r="F198" s="73"/>
-      <c r="G198" s="73"/>
-      <c r="H198" s="73"/>
+      <c r="C198" s="66"/>
+      <c r="D198" s="79"/>
+      <c r="E198" s="80"/>
+      <c r="F198" s="80"/>
+      <c r="G198" s="80"/>
+      <c r="H198" s="80"/>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
       <c r="K198" s="24"/>
       <c r="L198" s="24"/>
     </row>
-    <row r="199" spans="1:12" ht="12.45">
-      <c r="A199" s="64"/>
-      <c r="B199" s="62"/>
-      <c r="C199" s="62"/>
-      <c r="D199" s="73"/>
-      <c r="E199" s="73"/>
-      <c r="F199" s="73"/>
-      <c r="G199" s="73"/>
-      <c r="H199" s="73"/>
+    <row r="199" spans="1:12">
+      <c r="A199" s="71"/>
+      <c r="B199" s="66"/>
+      <c r="C199" s="66"/>
+      <c r="D199" s="80"/>
+      <c r="E199" s="80"/>
+      <c r="F199" s="80"/>
+      <c r="G199" s="80"/>
+      <c r="H199" s="80"/>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
       <c r="K199" s="24"/>
       <c r="L199" s="24"/>
     </row>
-    <row r="200" spans="1:12" ht="12.45">
-      <c r="A200" s="70" t="s">
+    <row r="200" spans="1:12">
+      <c r="A200" s="77" t="s">
         <v>474</v>
       </c>
-      <c r="B200" s="70" t="s">
+      <c r="B200" s="77" t="s">
         <v>575</v>
       </c>
-      <c r="C200" s="64"/>
+      <c r="C200" s="71"/>
       <c r="D200" s="21"/>
       <c r="E200" s="22"/>
       <c r="F200" s="22"/>
@@ -10542,10 +10434,10 @@
       <c r="K200" s="24"/>
       <c r="L200" s="24"/>
     </row>
-    <row r="201" spans="1:12" ht="12.45">
-      <c r="A201" s="64"/>
-      <c r="B201" s="64"/>
-      <c r="C201" s="64"/>
+    <row r="201" spans="1:12">
+      <c r="A201" s="71"/>
+      <c r="B201" s="71"/>
+      <c r="C201" s="71"/>
       <c r="D201" s="21"/>
       <c r="E201" s="22"/>
       <c r="F201" s="22"/>
@@ -10556,7 +10448,7 @@
       <c r="K201" s="24"/>
       <c r="L201" s="24"/>
     </row>
-    <row r="202" spans="1:12" ht="12.45">
+    <row r="202" spans="1:12">
       <c r="A202" s="1"/>
       <c r="B202" s="21"/>
       <c r="C202" s="21"/>
@@ -10570,7 +10462,7 @@
       <c r="K202" s="24"/>
       <c r="L202" s="24"/>
     </row>
-    <row r="203" spans="1:12" ht="12.45">
+    <row r="203" spans="1:12">
       <c r="A203" s="1"/>
       <c r="B203" s="21"/>
       <c r="C203" s="21"/>
@@ -10584,7 +10476,7 @@
       <c r="K203" s="24"/>
       <c r="L203" s="24"/>
     </row>
-    <row r="204" spans="1:12" ht="12.45">
+    <row r="204" spans="1:12">
       <c r="A204" s="1"/>
       <c r="B204" s="24"/>
       <c r="C204" s="24"/>
@@ -10598,7 +10490,7 @@
       <c r="K204" s="24"/>
       <c r="L204" s="24"/>
     </row>
-    <row r="205" spans="1:12" ht="12.45">
+    <row r="205" spans="1:12">
       <c r="A205" s="1"/>
       <c r="B205" s="24"/>
       <c r="C205" s="24"/>
@@ -10612,7 +10504,7 @@
       <c r="K205" s="24"/>
       <c r="L205" s="24"/>
     </row>
-    <row r="206" spans="1:12" ht="12.45">
+    <row r="206" spans="1:12">
       <c r="A206" s="1"/>
       <c r="B206" s="24"/>
       <c r="C206" s="24"/>
@@ -10626,7 +10518,7 @@
       <c r="K206" s="24"/>
       <c r="L206" s="24"/>
     </row>
-    <row r="207" spans="1:12" ht="12.45">
+    <row r="207" spans="1:12">
       <c r="A207" s="1"/>
       <c r="B207" s="24"/>
       <c r="C207" s="24"/>
@@ -10640,7 +10532,7 @@
       <c r="K207" s="24"/>
       <c r="L207" s="24"/>
     </row>
-    <row r="208" spans="1:12" ht="12.45">
+    <row r="208" spans="1:12">
       <c r="A208" s="1"/>
       <c r="B208" s="24"/>
       <c r="C208" s="24"/>
@@ -10654,7 +10546,7 @@
       <c r="K208" s="24"/>
       <c r="L208" s="24"/>
     </row>
-    <row r="209" spans="1:12" ht="12.45">
+    <row r="209" spans="1:12">
       <c r="A209" s="1"/>
       <c r="B209" s="24"/>
       <c r="C209" s="24"/>
@@ -10668,7 +10560,7 @@
       <c r="K209" s="24"/>
       <c r="L209" s="24"/>
     </row>
-    <row r="210" spans="1:12" ht="12.45">
+    <row r="210" spans="1:12">
       <c r="A210" s="1"/>
       <c r="B210" s="24"/>
       <c r="C210" s="24"/>
@@ -10682,7 +10574,7 @@
       <c r="K210" s="24"/>
       <c r="L210" s="24"/>
     </row>
-    <row r="211" spans="1:12" ht="12.45">
+    <row r="211" spans="1:12">
       <c r="A211" s="1"/>
       <c r="B211" s="24"/>
       <c r="C211" s="24"/>
@@ -10696,7 +10588,7 @@
       <c r="K211" s="24"/>
       <c r="L211" s="24"/>
     </row>
-    <row r="212" spans="1:12" ht="12.45">
+    <row r="212" spans="1:12">
       <c r="A212" s="1"/>
       <c r="B212" s="24"/>
       <c r="C212" s="24"/>
@@ -10710,7 +10602,7 @@
       <c r="K212" s="24"/>
       <c r="L212" s="24"/>
     </row>
-    <row r="213" spans="1:12" ht="12.45">
+    <row r="213" spans="1:12">
       <c r="A213" s="1"/>
       <c r="B213" s="24"/>
       <c r="C213" s="24"/>
@@ -10724,7 +10616,7 @@
       <c r="K213" s="24"/>
       <c r="L213" s="24"/>
     </row>
-    <row r="214" spans="1:12" ht="12.45">
+    <row r="214" spans="1:12">
       <c r="A214" s="1"/>
       <c r="B214" s="24"/>
       <c r="C214" s="24"/>
@@ -10738,7 +10630,7 @@
       <c r="K214" s="24"/>
       <c r="L214" s="24"/>
     </row>
-    <row r="215" spans="1:12" ht="12.45">
+    <row r="215" spans="1:12">
       <c r="A215" s="1"/>
       <c r="B215" s="24"/>
       <c r="C215" s="24"/>
@@ -10752,7 +10644,7 @@
       <c r="K215" s="24"/>
       <c r="L215" s="24"/>
     </row>
-    <row r="216" spans="1:12" ht="12.45">
+    <row r="216" spans="1:12">
       <c r="A216" s="1"/>
       <c r="B216" s="24"/>
       <c r="C216" s="24"/>
@@ -10766,7 +10658,7 @@
       <c r="K216" s="24"/>
       <c r="L216" s="24"/>
     </row>
-    <row r="217" spans="1:12" ht="12.45">
+    <row r="217" spans="1:12">
       <c r="A217" s="1"/>
       <c r="B217" s="24"/>
       <c r="C217" s="24"/>
@@ -10780,7 +10672,7 @@
       <c r="K217" s="24"/>
       <c r="L217" s="24"/>
     </row>
-    <row r="218" spans="1:12" ht="12.45">
+    <row r="218" spans="1:12">
       <c r="A218" s="1"/>
       <c r="B218" s="24"/>
       <c r="C218" s="24"/>
@@ -10794,7 +10686,7 @@
       <c r="K218" s="24"/>
       <c r="L218" s="24"/>
     </row>
-    <row r="219" spans="1:12" ht="12.45">
+    <row r="219" spans="1:12">
       <c r="A219" s="1"/>
       <c r="B219" s="24"/>
       <c r="C219" s="24"/>
@@ -10808,7 +10700,7 @@
       <c r="K219" s="24"/>
       <c r="L219" s="24"/>
     </row>
-    <row r="220" spans="1:12" ht="12.45">
+    <row r="220" spans="1:12">
       <c r="A220" s="1"/>
       <c r="B220" s="24"/>
       <c r="C220" s="24"/>
@@ -10822,7 +10714,7 @@
       <c r="K220" s="24"/>
       <c r="L220" s="24"/>
     </row>
-    <row r="221" spans="1:12" ht="12.45">
+    <row r="221" spans="1:12">
       <c r="A221" s="1"/>
       <c r="B221" s="24"/>
       <c r="C221" s="24"/>
@@ -10836,7 +10728,7 @@
       <c r="K221" s="24"/>
       <c r="L221" s="24"/>
     </row>
-    <row r="222" spans="1:12" ht="12.45">
+    <row r="222" spans="1:12">
       <c r="A222" s="1"/>
       <c r="B222" s="24"/>
       <c r="C222" s="24"/>
@@ -10850,7 +10742,7 @@
       <c r="K222" s="24"/>
       <c r="L222" s="24"/>
     </row>
-    <row r="223" spans="1:12" ht="12.45">
+    <row r="223" spans="1:12">
       <c r="A223" s="1"/>
       <c r="B223" s="24"/>
       <c r="C223" s="24"/>
@@ -10864,7 +10756,7 @@
       <c r="K223" s="24"/>
       <c r="L223" s="24"/>
     </row>
-    <row r="224" spans="1:12" ht="12.45">
+    <row r="224" spans="1:12">
       <c r="A224" s="1"/>
       <c r="B224" s="24"/>
       <c r="C224" s="24"/>
@@ -10878,7 +10770,7 @@
       <c r="K224" s="24"/>
       <c r="L224" s="24"/>
     </row>
-    <row r="225" spans="1:12" ht="12.45">
+    <row r="225" spans="1:12">
       <c r="A225" s="1"/>
       <c r="B225" s="24"/>
       <c r="C225" s="24"/>
@@ -10892,7 +10784,7 @@
       <c r="K225" s="24"/>
       <c r="L225" s="24"/>
     </row>
-    <row r="226" spans="1:12" ht="12.45">
+    <row r="226" spans="1:12">
       <c r="A226" s="1"/>
       <c r="B226" s="24"/>
       <c r="C226" s="24"/>
@@ -10906,7 +10798,7 @@
       <c r="K226" s="24"/>
       <c r="L226" s="24"/>
     </row>
-    <row r="227" spans="1:12" ht="12.45">
+    <row r="227" spans="1:12">
       <c r="A227" s="1"/>
       <c r="B227" s="24"/>
       <c r="C227" s="24"/>
@@ -10920,7 +10812,7 @@
       <c r="K227" s="24"/>
       <c r="L227" s="24"/>
     </row>
-    <row r="228" spans="1:12" ht="12.45">
+    <row r="228" spans="1:12">
       <c r="A228" s="1"/>
       <c r="B228" s="24"/>
       <c r="C228" s="24"/>
@@ -11063,126 +10955,126 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:J208"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-    <col min="4" max="4" width="7.58203125" customWidth="1"/>
-    <col min="5" max="5" width="56.6640625" customWidth="1"/>
-    <col min="6" max="6" width="53.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="63.33203125" customWidth="1"/>
-    <col min="9" max="10" width="11.58203125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="5" width="56.6328125" customWidth="1"/>
+    <col min="6" max="6" width="53.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" customWidth="1"/>
+    <col min="8" max="8" width="63.36328125" customWidth="1"/>
+    <col min="9" max="10" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12.45">
+    <row r="1" spans="1:10">
       <c r="A1" s="41"/>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="86" t="s">
         <v>668</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
       <c r="J1" s="41"/>
     </row>
-    <row r="2" spans="1:10" ht="12.45">
+    <row r="2" spans="1:10">
       <c r="A2" s="41"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
       <c r="H2" s="41"/>
       <c r="I2" s="41"/>
       <c r="J2" s="41"/>
     </row>
-    <row r="3" spans="1:10" ht="12.45">
+    <row r="3" spans="1:10">
       <c r="A3" s="41"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
       <c r="J3" s="41"/>
     </row>
-    <row r="4" spans="1:10" ht="12.45">
+    <row r="4" spans="1:10">
       <c r="A4" s="41"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="H4" s="41"/>
       <c r="I4" s="41"/>
       <c r="J4" s="41"/>
     </row>
-    <row r="5" spans="1:10" ht="12.45">
+    <row r="5" spans="1:10">
       <c r="A5" s="41"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
       <c r="H5" s="41"/>
       <c r="I5" s="41"/>
       <c r="J5" s="41"/>
     </row>
-    <row r="6" spans="1:10" ht="12.45">
+    <row r="6" spans="1:10">
       <c r="A6" s="41"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
       <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1">
       <c r="A7" s="41"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
       <c r="H7" s="41"/>
       <c r="I7" s="41"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="14">
       <c r="A8" s="41"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="67" t="s">
         <v>582</v>
       </c>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
       <c r="G8" s="42"/>
       <c r="H8" s="41"/>
       <c r="I8" s="41"/>
       <c r="J8" s="41"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="14">
       <c r="A9" s="41"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
       <c r="G9" s="42"/>
       <c r="H9" s="41"/>
       <c r="I9" s="41"/>
@@ -11226,8 +11118,8 @@
       <c r="I11" s="50"/>
       <c r="J11" s="50"/>
     </row>
-    <row r="12" spans="1:10" ht="138.9">
-      <c r="A12" s="77" t="s">
+    <row r="12" spans="1:10" ht="132">
+      <c r="A12" s="81" t="s">
         <v>583</v>
       </c>
       <c r="B12" s="51">
@@ -11254,8 +11146,8 @@
       <c r="I12" s="50"/>
       <c r="J12" s="50"/>
     </row>
-    <row r="13" spans="1:10" ht="12.45">
-      <c r="A13" s="78"/>
+    <row r="13" spans="1:10">
+      <c r="A13" s="82"/>
       <c r="B13" s="51">
         <v>44198</v>
       </c>
@@ -11268,8 +11160,8 @@
       <c r="I13" s="50"/>
       <c r="J13" s="50"/>
     </row>
-    <row r="14" spans="1:10" ht="12.45">
-      <c r="A14" s="78"/>
+    <row r="14" spans="1:10">
+      <c r="A14" s="82"/>
       <c r="B14" s="51">
         <v>44199</v>
       </c>
@@ -11282,8 +11174,8 @@
       <c r="I14" s="50"/>
       <c r="J14" s="50"/>
     </row>
-    <row r="15" spans="1:10" ht="12.45">
-      <c r="A15" s="78"/>
+    <row r="15" spans="1:10">
+      <c r="A15" s="82"/>
       <c r="B15" s="51">
         <v>44200</v>
       </c>
@@ -11300,8 +11192,8 @@
       <c r="I15" s="50"/>
       <c r="J15" s="50"/>
     </row>
-    <row r="16" spans="1:10" ht="12.45">
-      <c r="A16" s="78"/>
+    <row r="16" spans="1:10">
+      <c r="A16" s="82"/>
       <c r="B16" s="51"/>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
@@ -11312,8 +11204,8 @@
       <c r="I16" s="50"/>
       <c r="J16" s="50"/>
     </row>
-    <row r="17" spans="1:10" ht="12.45">
-      <c r="A17" s="78"/>
+    <row r="17" spans="1:10">
+      <c r="A17" s="82"/>
       <c r="B17" s="51"/>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
@@ -11324,8 +11216,8 @@
       <c r="I17" s="50"/>
       <c r="J17" s="50"/>
     </row>
-    <row r="18" spans="1:10" ht="12.45">
-      <c r="A18" s="78"/>
+    <row r="18" spans="1:10">
+      <c r="A18" s="82"/>
       <c r="B18" s="51"/>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
@@ -11337,7 +11229,7 @@
       <c r="J18" s="50"/>
     </row>
     <row r="19" spans="1:10" ht="19" customHeight="1">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="81" t="s">
         <v>580</v>
       </c>
       <c r="B19" s="51"/>
@@ -11352,8 +11244,8 @@
       <c r="I19" s="50"/>
       <c r="J19" s="50"/>
     </row>
-    <row r="20" spans="1:10" ht="12.45">
-      <c r="A20" s="78"/>
+    <row r="20" spans="1:10">
+      <c r="A20" s="82"/>
       <c r="B20" s="51"/>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
@@ -11364,8 +11256,8 @@
       <c r="I20" s="50"/>
       <c r="J20" s="50"/>
     </row>
-    <row r="21" spans="1:10" ht="12.45">
-      <c r="A21" s="78"/>
+    <row r="21" spans="1:10">
+      <c r="A21" s="82"/>
       <c r="B21" s="51"/>
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
@@ -11376,8 +11268,8 @@
       <c r="I21" s="50"/>
       <c r="J21" s="50"/>
     </row>
-    <row r="22" spans="1:10" ht="12.45">
-      <c r="A22" s="78"/>
+    <row r="22" spans="1:10">
+      <c r="A22" s="82"/>
       <c r="B22" s="51"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
@@ -11388,8 +11280,8 @@
       <c r="I22" s="50"/>
       <c r="J22" s="50"/>
     </row>
-    <row r="23" spans="1:10" ht="12.45">
-      <c r="A23" s="78"/>
+    <row r="23" spans="1:10">
+      <c r="A23" s="82"/>
       <c r="B23" s="51"/>
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
@@ -11400,8 +11292,8 @@
       <c r="I23" s="50"/>
       <c r="J23" s="50"/>
     </row>
-    <row r="24" spans="1:10" ht="12.45">
-      <c r="A24" s="78"/>
+    <row r="24" spans="1:10">
+      <c r="A24" s="82"/>
       <c r="B24" s="51"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
@@ -11412,8 +11304,8 @@
       <c r="I24" s="50"/>
       <c r="J24" s="50"/>
     </row>
-    <row r="25" spans="1:10" ht="12.45">
-      <c r="A25" s="78"/>
+    <row r="25" spans="1:10">
+      <c r="A25" s="82"/>
       <c r="B25" s="51"/>
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
@@ -11425,7 +11317,7 @@
       <c r="J25" s="50"/>
     </row>
     <row r="26" spans="1:10" ht="19" customHeight="1">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="83" t="s">
         <v>581</v>
       </c>
       <c r="B26" s="51"/>
@@ -11438,8 +11330,8 @@
       <c r="I26" s="50"/>
       <c r="J26" s="50"/>
     </row>
-    <row r="27" spans="1:10" ht="12.45">
-      <c r="A27" s="78"/>
+    <row r="27" spans="1:10">
+      <c r="A27" s="82"/>
       <c r="B27" s="51"/>
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
@@ -11450,8 +11342,8 @@
       <c r="I27" s="50"/>
       <c r="J27" s="50"/>
     </row>
-    <row r="28" spans="1:10" ht="12.45">
-      <c r="A28" s="78"/>
+    <row r="28" spans="1:10">
+      <c r="A28" s="82"/>
       <c r="B28" s="51"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
@@ -11462,8 +11354,8 @@
       <c r="I28" s="50"/>
       <c r="J28" s="50"/>
     </row>
-    <row r="29" spans="1:10" ht="12.45">
-      <c r="A29" s="78"/>
+    <row r="29" spans="1:10">
+      <c r="A29" s="82"/>
       <c r="B29" s="51"/>
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
@@ -11474,8 +11366,8 @@
       <c r="I29" s="50"/>
       <c r="J29" s="50"/>
     </row>
-    <row r="30" spans="1:10" ht="12.45">
-      <c r="A30" s="78"/>
+    <row r="30" spans="1:10">
+      <c r="A30" s="82"/>
       <c r="B30" s="51"/>
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
@@ -11486,8 +11378,8 @@
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
     </row>
-    <row r="31" spans="1:10" ht="12.45">
-      <c r="A31" s="78"/>
+    <row r="31" spans="1:10">
+      <c r="A31" s="82"/>
       <c r="B31" s="51"/>
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
@@ -11498,8 +11390,8 @@
       <c r="I31" s="50"/>
       <c r="J31" s="50"/>
     </row>
-    <row r="32" spans="1:10" ht="12.45">
-      <c r="A32" s="78"/>
+    <row r="32" spans="1:10">
+      <c r="A32" s="82"/>
       <c r="B32" s="51"/>
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
@@ -11510,7 +11402,7 @@
       <c r="I32" s="50"/>
       <c r="J32" s="50"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" ht="14">
       <c r="A33" s="41"/>
       <c r="B33" s="42"/>
       <c r="C33" s="41"/>
@@ -11522,7 +11414,7 @@
       <c r="I33" s="41"/>
       <c r="J33" s="41"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" ht="14">
       <c r="A34" s="41"/>
       <c r="B34" s="41"/>
       <c r="C34" s="41"/>
@@ -11534,7 +11426,7 @@
       <c r="I34" s="41"/>
       <c r="J34" s="41"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" ht="14">
       <c r="A35" s="41"/>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
@@ -11546,7 +11438,7 @@
       <c r="I35" s="41"/>
       <c r="J35" s="41"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" ht="14">
       <c r="A36" s="41"/>
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
@@ -11558,7 +11450,7 @@
       <c r="I36" s="41"/>
       <c r="J36" s="41"/>
     </row>
-    <row r="37" spans="1:10" ht="12.45">
+    <row r="37" spans="1:10">
       <c r="A37" s="41"/>
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
@@ -11570,7 +11462,7 @@
       <c r="I37" s="41"/>
       <c r="J37" s="41"/>
     </row>
-    <row r="38" spans="1:10" ht="12.45">
+    <row r="38" spans="1:10">
       <c r="A38" s="41"/>
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
@@ -11582,7 +11474,7 @@
       <c r="I38" s="41"/>
       <c r="J38" s="41"/>
     </row>
-    <row r="39" spans="1:10" ht="12.45">
+    <row r="39" spans="1:10">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -11594,7 +11486,7 @@
       <c r="I39" s="41"/>
       <c r="J39" s="41"/>
     </row>
-    <row r="40" spans="1:10" ht="12.45">
+    <row r="40" spans="1:10">
       <c r="A40" s="41"/>
       <c r="B40" s="41"/>
       <c r="C40" s="41"/>
@@ -11606,7 +11498,7 @@
       <c r="I40" s="41"/>
       <c r="J40" s="41"/>
     </row>
-    <row r="41" spans="1:10" ht="12.45">
+    <row r="41" spans="1:10">
       <c r="A41" s="41"/>
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
@@ -11618,7 +11510,7 @@
       <c r="I41" s="41"/>
       <c r="J41" s="41"/>
     </row>
-    <row r="42" spans="1:10" ht="12.45">
+    <row r="42" spans="1:10">
       <c r="A42" s="41"/>
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
@@ -11630,7 +11522,7 @@
       <c r="I42" s="41"/>
       <c r="J42" s="41"/>
     </row>
-    <row r="43" spans="1:10" ht="12.45">
+    <row r="43" spans="1:10">
       <c r="A43" s="41"/>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
@@ -11642,7 +11534,7 @@
       <c r="I43" s="41"/>
       <c r="J43" s="41"/>
     </row>
-    <row r="44" spans="1:10" ht="12.45">
+    <row r="44" spans="1:10">
       <c r="A44" s="41"/>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -11654,7 +11546,7 @@
       <c r="I44" s="41"/>
       <c r="J44" s="41"/>
     </row>
-    <row r="45" spans="1:10" ht="12.45">
+    <row r="45" spans="1:10">
       <c r="A45" s="41"/>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -11666,7 +11558,7 @@
       <c r="I45" s="41"/>
       <c r="J45" s="41"/>
     </row>
-    <row r="46" spans="1:10" ht="12.45">
+    <row r="46" spans="1:10">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
@@ -11678,7 +11570,7 @@
       <c r="I46" s="41"/>
       <c r="J46" s="41"/>
     </row>
-    <row r="47" spans="1:10" ht="12.45">
+    <row r="47" spans="1:10">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
@@ -11690,7 +11582,7 @@
       <c r="I47" s="41"/>
       <c r="J47" s="41"/>
     </row>
-    <row r="48" spans="1:10" ht="12.45">
+    <row r="48" spans="1:10">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -11702,7 +11594,7 @@
       <c r="I48" s="41"/>
       <c r="J48" s="41"/>
     </row>
-    <row r="49" spans="1:10" ht="12.45">
+    <row r="49" spans="1:10">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
@@ -11714,7 +11606,7 @@
       <c r="I49" s="41"/>
       <c r="J49" s="41"/>
     </row>
-    <row r="50" spans="1:10" ht="12.45">
+    <row r="50" spans="1:10">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
@@ -11726,7 +11618,7 @@
       <c r="I50" s="41"/>
       <c r="J50" s="41"/>
     </row>
-    <row r="51" spans="1:10" ht="12.45">
+    <row r="51" spans="1:10">
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -11738,7 +11630,7 @@
       <c r="I51" s="41"/>
       <c r="J51" s="41"/>
     </row>
-    <row r="52" spans="1:10" ht="12.45">
+    <row r="52" spans="1:10">
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -11750,7 +11642,7 @@
       <c r="I52" s="41"/>
       <c r="J52" s="41"/>
     </row>
-    <row r="53" spans="1:10" ht="12.45">
+    <row r="53" spans="1:10">
       <c r="A53" s="41"/>
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
@@ -11762,7 +11654,7 @@
       <c r="I53" s="41"/>
       <c r="J53" s="41"/>
     </row>
-    <row r="54" spans="1:10" ht="12.45">
+    <row r="54" spans="1:10">
       <c r="A54" s="41"/>
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
@@ -11774,7 +11666,7 @@
       <c r="I54" s="41"/>
       <c r="J54" s="41"/>
     </row>
-    <row r="55" spans="1:10" ht="12.45">
+    <row r="55" spans="1:10">
       <c r="A55" s="41"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -11786,7 +11678,7 @@
       <c r="I55" s="41"/>
       <c r="J55" s="41"/>
     </row>
-    <row r="56" spans="1:10" ht="12.45">
+    <row r="56" spans="1:10">
       <c r="A56" s="41"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -11798,7 +11690,7 @@
       <c r="I56" s="41"/>
       <c r="J56" s="41"/>
     </row>
-    <row r="57" spans="1:10" ht="12.45">
+    <row r="57" spans="1:10">
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -11810,7 +11702,7 @@
       <c r="I57" s="41"/>
       <c r="J57" s="41"/>
     </row>
-    <row r="58" spans="1:10" ht="12.45">
+    <row r="58" spans="1:10">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
       <c r="C58" s="41"/>
@@ -11822,7 +11714,7 @@
       <c r="I58" s="41"/>
       <c r="J58" s="41"/>
     </row>
-    <row r="59" spans="1:10" ht="12.45">
+    <row r="59" spans="1:10">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
       <c r="C59" s="41"/>
@@ -11834,7 +11726,7 @@
       <c r="I59" s="41"/>
       <c r="J59" s="41"/>
     </row>
-    <row r="60" spans="1:10" ht="12.45">
+    <row r="60" spans="1:10">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="C60" s="41"/>
@@ -11846,7 +11738,7 @@
       <c r="I60" s="41"/>
       <c r="J60" s="41"/>
     </row>
-    <row r="61" spans="1:10" ht="12.45">
+    <row r="61" spans="1:10">
       <c r="A61" s="41"/>
       <c r="B61" s="41"/>
       <c r="C61" s="41"/>
@@ -11858,7 +11750,7 @@
       <c r="I61" s="41"/>
       <c r="J61" s="41"/>
     </row>
-    <row r="62" spans="1:10" ht="12.45">
+    <row r="62" spans="1:10">
       <c r="A62" s="41"/>
       <c r="B62" s="41"/>
       <c r="C62" s="41"/>
@@ -11870,7 +11762,7 @@
       <c r="I62" s="41"/>
       <c r="J62" s="41"/>
     </row>
-    <row r="63" spans="1:10" ht="12.45">
+    <row r="63" spans="1:10">
       <c r="A63" s="41"/>
       <c r="B63" s="41"/>
       <c r="C63" s="41"/>
@@ -11882,7 +11774,7 @@
       <c r="I63" s="41"/>
       <c r="J63" s="41"/>
     </row>
-    <row r="64" spans="1:10" ht="12.45">
+    <row r="64" spans="1:10">
       <c r="A64" s="41"/>
       <c r="B64" s="41"/>
       <c r="C64" s="41"/>
@@ -11894,7 +11786,7 @@
       <c r="I64" s="41"/>
       <c r="J64" s="41"/>
     </row>
-    <row r="65" spans="1:10" ht="12.45">
+    <row r="65" spans="1:10">
       <c r="A65" s="41"/>
       <c r="B65" s="41"/>
       <c r="C65" s="41"/>
@@ -11906,7 +11798,7 @@
       <c r="I65" s="41"/>
       <c r="J65" s="41"/>
     </row>
-    <row r="66" spans="1:10" ht="12.45">
+    <row r="66" spans="1:10">
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="C66" s="41"/>
@@ -11918,7 +11810,7 @@
       <c r="I66" s="41"/>
       <c r="J66" s="41"/>
     </row>
-    <row r="67" spans="1:10" ht="12.45">
+    <row r="67" spans="1:10">
       <c r="A67" s="41"/>
       <c r="B67" s="41"/>
       <c r="C67" s="41"/>
@@ -11930,7 +11822,7 @@
       <c r="I67" s="41"/>
       <c r="J67" s="41"/>
     </row>
-    <row r="68" spans="1:10" ht="12.45">
+    <row r="68" spans="1:10">
       <c r="A68" s="41"/>
       <c r="B68" s="41"/>
       <c r="C68" s="41"/>
@@ -11942,7 +11834,7 @@
       <c r="I68" s="41"/>
       <c r="J68" s="41"/>
     </row>
-    <row r="69" spans="1:10" ht="12.45">
+    <row r="69" spans="1:10">
       <c r="A69" s="41"/>
       <c r="B69" s="41"/>
       <c r="C69" s="41"/>
@@ -11954,7 +11846,7 @@
       <c r="I69" s="41"/>
       <c r="J69" s="41"/>
     </row>
-    <row r="70" spans="1:10" ht="12.45">
+    <row r="70" spans="1:10">
       <c r="A70" s="41"/>
       <c r="B70" s="41"/>
       <c r="C70" s="41"/>
@@ -11966,7 +11858,7 @@
       <c r="I70" s="41"/>
       <c r="J70" s="41"/>
     </row>
-    <row r="71" spans="1:10" ht="12.45">
+    <row r="71" spans="1:10">
       <c r="A71" s="41"/>
       <c r="B71" s="41"/>
       <c r="C71" s="41"/>
@@ -11978,7 +11870,7 @@
       <c r="I71" s="41"/>
       <c r="J71" s="41"/>
     </row>
-    <row r="72" spans="1:10" ht="12.45">
+    <row r="72" spans="1:10">
       <c r="A72" s="41"/>
       <c r="B72" s="41"/>
       <c r="C72" s="41"/>
@@ -11990,7 +11882,7 @@
       <c r="I72" s="41"/>
       <c r="J72" s="41"/>
     </row>
-    <row r="73" spans="1:10" ht="12.45">
+    <row r="73" spans="1:10">
       <c r="A73" s="41"/>
       <c r="B73" s="41"/>
       <c r="C73" s="41"/>
@@ -12002,7 +11894,7 @@
       <c r="I73" s="41"/>
       <c r="J73" s="41"/>
     </row>
-    <row r="74" spans="1:10" ht="12.45">
+    <row r="74" spans="1:10">
       <c r="A74" s="41"/>
       <c r="B74" s="41"/>
       <c r="C74" s="41"/>
@@ -12014,7 +11906,7 @@
       <c r="I74" s="41"/>
       <c r="J74" s="41"/>
     </row>
-    <row r="75" spans="1:10" ht="12.45">
+    <row r="75" spans="1:10">
       <c r="A75" s="41"/>
       <c r="B75" s="41"/>
       <c r="C75" s="41"/>
@@ -12026,7 +11918,7 @@
       <c r="I75" s="41"/>
       <c r="J75" s="41"/>
     </row>
-    <row r="76" spans="1:10" ht="12.45">
+    <row r="76" spans="1:10">
       <c r="A76" s="41"/>
       <c r="B76" s="41"/>
       <c r="C76" s="41"/>
@@ -12038,7 +11930,7 @@
       <c r="I76" s="41"/>
       <c r="J76" s="41"/>
     </row>
-    <row r="77" spans="1:10" ht="12.45">
+    <row r="77" spans="1:10">
       <c r="A77" s="41"/>
       <c r="B77" s="41"/>
       <c r="C77" s="41"/>
@@ -12050,7 +11942,7 @@
       <c r="I77" s="41"/>
       <c r="J77" s="41"/>
     </row>
-    <row r="78" spans="1:10" ht="12.45">
+    <row r="78" spans="1:10">
       <c r="A78" s="41"/>
       <c r="B78" s="41"/>
       <c r="C78" s="41"/>
@@ -12062,7 +11954,7 @@
       <c r="I78" s="41"/>
       <c r="J78" s="41"/>
     </row>
-    <row r="79" spans="1:10" ht="12.45">
+    <row r="79" spans="1:10">
       <c r="A79" s="41"/>
       <c r="B79" s="41"/>
       <c r="C79" s="41"/>
@@ -12074,7 +11966,7 @@
       <c r="I79" s="41"/>
       <c r="J79" s="41"/>
     </row>
-    <row r="80" spans="1:10" ht="12.45">
+    <row r="80" spans="1:10">
       <c r="A80" s="41"/>
       <c r="B80" s="41"/>
       <c r="C80" s="41"/>
@@ -12086,7 +11978,7 @@
       <c r="I80" s="41"/>
       <c r="J80" s="41"/>
     </row>
-    <row r="81" spans="1:10" ht="12.45">
+    <row r="81" spans="1:10">
       <c r="A81" s="41"/>
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
@@ -12098,7 +11990,7 @@
       <c r="I81" s="41"/>
       <c r="J81" s="41"/>
     </row>
-    <row r="82" spans="1:10" ht="12.45">
+    <row r="82" spans="1:10">
       <c r="A82" s="41"/>
       <c r="B82" s="41"/>
       <c r="C82" s="41"/>
@@ -12110,7 +12002,7 @@
       <c r="I82" s="41"/>
       <c r="J82" s="41"/>
     </row>
-    <row r="83" spans="1:10" ht="12.45">
+    <row r="83" spans="1:10">
       <c r="A83" s="41"/>
       <c r="B83" s="41"/>
       <c r="C83" s="41"/>
@@ -12122,7 +12014,7 @@
       <c r="I83" s="41"/>
       <c r="J83" s="41"/>
     </row>
-    <row r="84" spans="1:10" ht="12.45">
+    <row r="84" spans="1:10">
       <c r="A84" s="41"/>
       <c r="B84" s="41"/>
       <c r="C84" s="41"/>
@@ -12134,7 +12026,7 @@
       <c r="I84" s="41"/>
       <c r="J84" s="41"/>
     </row>
-    <row r="85" spans="1:10" ht="12.45">
+    <row r="85" spans="1:10">
       <c r="A85" s="41"/>
       <c r="B85" s="41"/>
       <c r="C85" s="41"/>
@@ -12146,7 +12038,7 @@
       <c r="I85" s="41"/>
       <c r="J85" s="41"/>
     </row>
-    <row r="86" spans="1:10" ht="12.45">
+    <row r="86" spans="1:10">
       <c r="A86" s="41"/>
       <c r="B86" s="41"/>
       <c r="C86" s="41"/>
@@ -12158,7 +12050,7 @@
       <c r="I86" s="41"/>
       <c r="J86" s="41"/>
     </row>
-    <row r="87" spans="1:10" ht="12.45">
+    <row r="87" spans="1:10">
       <c r="A87" s="41"/>
       <c r="B87" s="41"/>
       <c r="C87" s="41"/>
@@ -12170,7 +12062,7 @@
       <c r="I87" s="41"/>
       <c r="J87" s="41"/>
     </row>
-    <row r="88" spans="1:10" ht="12.45">
+    <row r="88" spans="1:10">
       <c r="A88" s="41"/>
       <c r="B88" s="41"/>
       <c r="C88" s="41"/>
@@ -12182,7 +12074,7 @@
       <c r="I88" s="41"/>
       <c r="J88" s="41"/>
     </row>
-    <row r="89" spans="1:10" ht="12.45">
+    <row r="89" spans="1:10">
       <c r="A89" s="41"/>
       <c r="B89" s="41"/>
       <c r="C89" s="41"/>
@@ -12194,7 +12086,7 @@
       <c r="I89" s="41"/>
       <c r="J89" s="41"/>
     </row>
-    <row r="90" spans="1:10" ht="12.45">
+    <row r="90" spans="1:10">
       <c r="A90" s="41"/>
       <c r="B90" s="41"/>
       <c r="C90" s="41"/>
@@ -12206,7 +12098,7 @@
       <c r="I90" s="41"/>
       <c r="J90" s="41"/>
     </row>
-    <row r="91" spans="1:10" ht="12.45">
+    <row r="91" spans="1:10">
       <c r="A91" s="41"/>
       <c r="B91" s="41"/>
       <c r="C91" s="41"/>
@@ -12218,7 +12110,7 @@
       <c r="I91" s="41"/>
       <c r="J91" s="41"/>
     </row>
-    <row r="92" spans="1:10" ht="12.45">
+    <row r="92" spans="1:10">
       <c r="A92" s="41"/>
       <c r="B92" s="41"/>
       <c r="C92" s="41"/>
@@ -12230,7 +12122,7 @@
       <c r="I92" s="41"/>
       <c r="J92" s="41"/>
     </row>
-    <row r="93" spans="1:10" ht="12.45">
+    <row r="93" spans="1:10">
       <c r="A93" s="41"/>
       <c r="B93" s="41"/>
       <c r="C93" s="41"/>
@@ -12242,7 +12134,7 @@
       <c r="I93" s="41"/>
       <c r="J93" s="41"/>
     </row>
-    <row r="94" spans="1:10" ht="12.45">
+    <row r="94" spans="1:10">
       <c r="A94" s="41"/>
       <c r="B94" s="41"/>
       <c r="C94" s="41"/>
@@ -12254,7 +12146,7 @@
       <c r="I94" s="41"/>
       <c r="J94" s="41"/>
     </row>
-    <row r="95" spans="1:10" ht="12.45">
+    <row r="95" spans="1:10">
       <c r="A95" s="41"/>
       <c r="B95" s="41"/>
       <c r="C95" s="41"/>
@@ -12266,7 +12158,7 @@
       <c r="I95" s="41"/>
       <c r="J95" s="41"/>
     </row>
-    <row r="96" spans="1:10" ht="12.45">
+    <row r="96" spans="1:10">
       <c r="A96" s="41"/>
       <c r="B96" s="41"/>
       <c r="C96" s="41"/>
@@ -12278,7 +12170,7 @@
       <c r="I96" s="41"/>
       <c r="J96" s="41"/>
     </row>
-    <row r="97" spans="1:10" ht="12.45">
+    <row r="97" spans="1:10">
       <c r="A97" s="41"/>
       <c r="B97" s="41"/>
       <c r="C97" s="41"/>
@@ -12290,7 +12182,7 @@
       <c r="I97" s="41"/>
       <c r="J97" s="41"/>
     </row>
-    <row r="98" spans="1:10" ht="12.45">
+    <row r="98" spans="1:10">
       <c r="A98" s="41"/>
       <c r="B98" s="41"/>
       <c r="C98" s="41"/>
@@ -12302,7 +12194,7 @@
       <c r="I98" s="41"/>
       <c r="J98" s="41"/>
     </row>
-    <row r="99" spans="1:10" ht="12.45">
+    <row r="99" spans="1:10">
       <c r="A99" s="41"/>
       <c r="B99" s="41"/>
       <c r="C99" s="41"/>
@@ -12314,7 +12206,7 @@
       <c r="I99" s="41"/>
       <c r="J99" s="41"/>
     </row>
-    <row r="100" spans="1:10" ht="12.45">
+    <row r="100" spans="1:10">
       <c r="A100" s="41"/>
       <c r="B100" s="41"/>
       <c r="C100" s="41"/>
@@ -12326,7 +12218,7 @@
       <c r="I100" s="41"/>
       <c r="J100" s="41"/>
     </row>
-    <row r="101" spans="1:10" ht="12.45">
+    <row r="101" spans="1:10">
       <c r="A101" s="41"/>
       <c r="B101" s="41"/>
       <c r="C101" s="41"/>
@@ -12338,7 +12230,7 @@
       <c r="I101" s="41"/>
       <c r="J101" s="41"/>
     </row>
-    <row r="102" spans="1:10" ht="12.45">
+    <row r="102" spans="1:10">
       <c r="A102" s="41"/>
       <c r="B102" s="41"/>
       <c r="C102" s="41"/>
@@ -12350,7 +12242,7 @@
       <c r="I102" s="41"/>
       <c r="J102" s="41"/>
     </row>
-    <row r="103" spans="1:10" ht="12.45">
+    <row r="103" spans="1:10">
       <c r="A103" s="41"/>
       <c r="B103" s="41"/>
       <c r="C103" s="41"/>
@@ -12362,7 +12254,7 @@
       <c r="I103" s="41"/>
       <c r="J103" s="41"/>
     </row>
-    <row r="104" spans="1:10" ht="12.45">
+    <row r="104" spans="1:10">
       <c r="A104" s="41"/>
       <c r="B104" s="41"/>
       <c r="C104" s="41"/>
@@ -12374,7 +12266,7 @@
       <c r="I104" s="41"/>
       <c r="J104" s="41"/>
     </row>
-    <row r="105" spans="1:10" ht="12.45">
+    <row r="105" spans="1:10">
       <c r="A105" s="41"/>
       <c r="B105" s="41"/>
       <c r="C105" s="41"/>
@@ -12386,7 +12278,7 @@
       <c r="I105" s="41"/>
       <c r="J105" s="41"/>
     </row>
-    <row r="106" spans="1:10" ht="12.45">
+    <row r="106" spans="1:10">
       <c r="A106" s="41"/>
       <c r="B106" s="41"/>
       <c r="C106" s="41"/>
@@ -12398,7 +12290,7 @@
       <c r="I106" s="41"/>
       <c r="J106" s="41"/>
     </row>
-    <row r="107" spans="1:10" ht="12.45">
+    <row r="107" spans="1:10">
       <c r="A107" s="41"/>
       <c r="B107" s="41"/>
       <c r="C107" s="41"/>
@@ -12410,7 +12302,7 @@
       <c r="I107" s="41"/>
       <c r="J107" s="41"/>
     </row>
-    <row r="108" spans="1:10" ht="12.45">
+    <row r="108" spans="1:10">
       <c r="A108" s="41"/>
       <c r="B108" s="41"/>
       <c r="C108" s="41"/>
@@ -12422,7 +12314,7 @@
       <c r="I108" s="41"/>
       <c r="J108" s="41"/>
     </row>
-    <row r="109" spans="1:10" ht="12.45">
+    <row r="109" spans="1:10">
       <c r="A109" s="41"/>
       <c r="B109" s="41"/>
       <c r="C109" s="41"/>
@@ -12434,7 +12326,7 @@
       <c r="I109" s="41"/>
       <c r="J109" s="41"/>
     </row>
-    <row r="110" spans="1:10" ht="12.45">
+    <row r="110" spans="1:10">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
       <c r="C110" s="41"/>
@@ -12446,7 +12338,7 @@
       <c r="I110" s="41"/>
       <c r="J110" s="41"/>
     </row>
-    <row r="111" spans="1:10" ht="12.45">
+    <row r="111" spans="1:10">
       <c r="A111" s="41"/>
       <c r="B111" s="41"/>
       <c r="C111" s="41"/>
@@ -12458,7 +12350,7 @@
       <c r="I111" s="41"/>
       <c r="J111" s="41"/>
     </row>
-    <row r="112" spans="1:10" ht="12.45">
+    <row r="112" spans="1:10">
       <c r="A112" s="41"/>
       <c r="B112" s="41"/>
       <c r="C112" s="41"/>
@@ -12470,7 +12362,7 @@
       <c r="I112" s="41"/>
       <c r="J112" s="41"/>
     </row>
-    <row r="113" spans="1:10" ht="12.45">
+    <row r="113" spans="1:10">
       <c r="A113" s="41"/>
       <c r="B113" s="41"/>
       <c r="C113" s="41"/>
@@ -12482,7 +12374,7 @@
       <c r="I113" s="41"/>
       <c r="J113" s="41"/>
     </row>
-    <row r="114" spans="1:10" ht="12.45">
+    <row r="114" spans="1:10">
       <c r="A114" s="41"/>
       <c r="B114" s="41"/>
       <c r="C114" s="41"/>
@@ -12494,7 +12386,7 @@
       <c r="I114" s="41"/>
       <c r="J114" s="41"/>
     </row>
-    <row r="115" spans="1:10" ht="12.45">
+    <row r="115" spans="1:10">
       <c r="A115" s="41"/>
       <c r="B115" s="41"/>
       <c r="C115" s="41"/>
@@ -12506,7 +12398,7 @@
       <c r="I115" s="41"/>
       <c r="J115" s="41"/>
     </row>
-    <row r="116" spans="1:10" ht="12.45">
+    <row r="116" spans="1:10">
       <c r="A116" s="41"/>
       <c r="B116" s="41"/>
       <c r="C116" s="41"/>
@@ -12518,7 +12410,7 @@
       <c r="I116" s="41"/>
       <c r="J116" s="41"/>
     </row>
-    <row r="117" spans="1:10" ht="12.45">
+    <row r="117" spans="1:10">
       <c r="A117" s="41"/>
       <c r="B117" s="41"/>
       <c r="C117" s="41"/>
@@ -12530,7 +12422,7 @@
       <c r="I117" s="41"/>
       <c r="J117" s="41"/>
     </row>
-    <row r="118" spans="1:10" ht="12.45">
+    <row r="118" spans="1:10">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
       <c r="C118" s="41"/>
@@ -12542,7 +12434,7 @@
       <c r="I118" s="41"/>
       <c r="J118" s="41"/>
     </row>
-    <row r="119" spans="1:10" ht="12.45">
+    <row r="119" spans="1:10">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
       <c r="C119" s="41"/>
@@ -12554,7 +12446,7 @@
       <c r="I119" s="41"/>
       <c r="J119" s="41"/>
     </row>
-    <row r="120" spans="1:10" ht="12.45">
+    <row r="120" spans="1:10">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
       <c r="C120" s="41"/>
@@ -12566,7 +12458,7 @@
       <c r="I120" s="41"/>
       <c r="J120" s="41"/>
     </row>
-    <row r="121" spans="1:10" ht="12.45">
+    <row r="121" spans="1:10">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
       <c r="C121" s="41"/>
@@ -12578,7 +12470,7 @@
       <c r="I121" s="41"/>
       <c r="J121" s="41"/>
     </row>
-    <row r="122" spans="1:10" ht="12.45">
+    <row r="122" spans="1:10">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
       <c r="C122" s="41"/>
@@ -12590,7 +12482,7 @@
       <c r="I122" s="41"/>
       <c r="J122" s="41"/>
     </row>
-    <row r="123" spans="1:10" ht="12.45">
+    <row r="123" spans="1:10">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
       <c r="C123" s="41"/>
@@ -12602,7 +12494,7 @@
       <c r="I123" s="41"/>
       <c r="J123" s="41"/>
     </row>
-    <row r="124" spans="1:10" ht="12.45">
+    <row r="124" spans="1:10">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
       <c r="C124" s="41"/>
@@ -12614,7 +12506,7 @@
       <c r="I124" s="41"/>
       <c r="J124" s="41"/>
     </row>
-    <row r="125" spans="1:10" ht="12.45">
+    <row r="125" spans="1:10">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
       <c r="C125" s="41"/>
@@ -12626,7 +12518,7 @@
       <c r="I125" s="41"/>
       <c r="J125" s="41"/>
     </row>
-    <row r="126" spans="1:10" ht="12.45">
+    <row r="126" spans="1:10">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="41"/>
@@ -12638,7 +12530,7 @@
       <c r="I126" s="41"/>
       <c r="J126" s="41"/>
     </row>
-    <row r="127" spans="1:10" ht="12.45">
+    <row r="127" spans="1:10">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
       <c r="C127" s="41"/>
@@ -12650,7 +12542,7 @@
       <c r="I127" s="41"/>
       <c r="J127" s="41"/>
     </row>
-    <row r="128" spans="1:10" ht="12.45">
+    <row r="128" spans="1:10">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
       <c r="C128" s="41"/>
@@ -12662,7 +12554,7 @@
       <c r="I128" s="41"/>
       <c r="J128" s="41"/>
     </row>
-    <row r="129" spans="1:10" ht="12.45">
+    <row r="129" spans="1:10">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
       <c r="C129" s="41"/>
@@ -12674,7 +12566,7 @@
       <c r="I129" s="41"/>
       <c r="J129" s="41"/>
     </row>
-    <row r="130" spans="1:10" ht="12.45">
+    <row r="130" spans="1:10">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
       <c r="C130" s="41"/>
@@ -12686,7 +12578,7 @@
       <c r="I130" s="41"/>
       <c r="J130" s="41"/>
     </row>
-    <row r="131" spans="1:10" ht="12.45">
+    <row r="131" spans="1:10">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
       <c r="C131" s="41"/>
@@ -12698,7 +12590,7 @@
       <c r="I131" s="41"/>
       <c r="J131" s="41"/>
     </row>
-    <row r="132" spans="1:10" ht="12.45">
+    <row r="132" spans="1:10">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
       <c r="C132" s="41"/>
@@ -12710,7 +12602,7 @@
       <c r="I132" s="41"/>
       <c r="J132" s="41"/>
     </row>
-    <row r="133" spans="1:10" ht="12.45">
+    <row r="133" spans="1:10">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
       <c r="C133" s="41"/>
@@ -12722,7 +12614,7 @@
       <c r="I133" s="41"/>
       <c r="J133" s="41"/>
     </row>
-    <row r="134" spans="1:10" ht="12.45">
+    <row r="134" spans="1:10">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
       <c r="C134" s="41"/>
@@ -12734,7 +12626,7 @@
       <c r="I134" s="41"/>
       <c r="J134" s="41"/>
     </row>
-    <row r="135" spans="1:10" ht="12.45">
+    <row r="135" spans="1:10">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
       <c r="C135" s="41"/>
@@ -12746,7 +12638,7 @@
       <c r="I135" s="41"/>
       <c r="J135" s="41"/>
     </row>
-    <row r="136" spans="1:10" ht="12.45">
+    <row r="136" spans="1:10">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
       <c r="C136" s="41"/>
@@ -12758,7 +12650,7 @@
       <c r="I136" s="41"/>
       <c r="J136" s="41"/>
     </row>
-    <row r="137" spans="1:10" ht="12.45">
+    <row r="137" spans="1:10">
       <c r="A137" s="41"/>
       <c r="B137" s="41"/>
       <c r="C137" s="41"/>
@@ -12770,7 +12662,7 @@
       <c r="I137" s="41"/>
       <c r="J137" s="41"/>
     </row>
-    <row r="138" spans="1:10" ht="12.45">
+    <row r="138" spans="1:10">
       <c r="A138" s="41"/>
       <c r="B138" s="41"/>
       <c r="C138" s="41"/>
@@ -12782,7 +12674,7 @@
       <c r="I138" s="41"/>
       <c r="J138" s="41"/>
     </row>
-    <row r="139" spans="1:10" ht="12.45">
+    <row r="139" spans="1:10">
       <c r="A139" s="41"/>
       <c r="B139" s="41"/>
       <c r="C139" s="41"/>
@@ -12794,7 +12686,7 @@
       <c r="I139" s="41"/>
       <c r="J139" s="41"/>
     </row>
-    <row r="140" spans="1:10" ht="12.45">
+    <row r="140" spans="1:10">
       <c r="A140" s="41"/>
       <c r="B140" s="41"/>
       <c r="C140" s="41"/>
@@ -12806,7 +12698,7 @@
       <c r="I140" s="41"/>
       <c r="J140" s="41"/>
     </row>
-    <row r="141" spans="1:10" ht="12.45">
+    <row r="141" spans="1:10">
       <c r="A141" s="41"/>
       <c r="B141" s="41"/>
       <c r="C141" s="41"/>
@@ -12818,7 +12710,7 @@
       <c r="I141" s="41"/>
       <c r="J141" s="41"/>
     </row>
-    <row r="142" spans="1:10" ht="12.45">
+    <row r="142" spans="1:10">
       <c r="A142" s="41"/>
       <c r="B142" s="41"/>
       <c r="C142" s="41"/>
@@ -12830,7 +12722,7 @@
       <c r="I142" s="41"/>
       <c r="J142" s="41"/>
     </row>
-    <row r="143" spans="1:10" ht="12.45">
+    <row r="143" spans="1:10">
       <c r="A143" s="41"/>
       <c r="B143" s="41"/>
       <c r="C143" s="41"/>
@@ -12842,7 +12734,7 @@
       <c r="I143" s="41"/>
       <c r="J143" s="41"/>
     </row>
-    <row r="144" spans="1:10" ht="12.45">
+    <row r="144" spans="1:10">
       <c r="A144" s="41"/>
       <c r="B144" s="41"/>
       <c r="C144" s="41"/>
@@ -12854,7 +12746,7 @@
       <c r="I144" s="41"/>
       <c r="J144" s="41"/>
     </row>
-    <row r="145" spans="1:10" ht="12.45">
+    <row r="145" spans="1:10">
       <c r="A145" s="41"/>
       <c r="B145" s="41"/>
       <c r="C145" s="41"/>
@@ -12866,7 +12758,7 @@
       <c r="I145" s="41"/>
       <c r="J145" s="41"/>
     </row>
-    <row r="146" spans="1:10" ht="12.45">
+    <row r="146" spans="1:10">
       <c r="A146" s="41"/>
       <c r="B146" s="41"/>
       <c r="C146" s="41"/>
@@ -12878,7 +12770,7 @@
       <c r="I146" s="41"/>
       <c r="J146" s="41"/>
     </row>
-    <row r="147" spans="1:10" ht="12.45">
+    <row r="147" spans="1:10">
       <c r="A147" s="41"/>
       <c r="B147" s="41"/>
       <c r="C147" s="41"/>
@@ -12890,7 +12782,7 @@
       <c r="I147" s="41"/>
       <c r="J147" s="41"/>
     </row>
-    <row r="148" spans="1:10" ht="12.45">
+    <row r="148" spans="1:10">
       <c r="A148" s="41"/>
       <c r="B148" s="41"/>
       <c r="C148" s="41"/>
@@ -12902,7 +12794,7 @@
       <c r="I148" s="41"/>
       <c r="J148" s="41"/>
     </row>
-    <row r="149" spans="1:10" ht="12.45">
+    <row r="149" spans="1:10">
       <c r="A149" s="41"/>
       <c r="B149" s="41"/>
       <c r="C149" s="41"/>
@@ -12914,7 +12806,7 @@
       <c r="I149" s="41"/>
       <c r="J149" s="41"/>
     </row>
-    <row r="150" spans="1:10" ht="12.45">
+    <row r="150" spans="1:10">
       <c r="A150" s="41"/>
       <c r="B150" s="41"/>
       <c r="C150" s="41"/>
@@ -12926,7 +12818,7 @@
       <c r="I150" s="41"/>
       <c r="J150" s="41"/>
     </row>
-    <row r="151" spans="1:10" ht="12.45">
+    <row r="151" spans="1:10">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
       <c r="C151" s="41"/>
@@ -12938,7 +12830,7 @@
       <c r="I151" s="41"/>
       <c r="J151" s="41"/>
     </row>
-    <row r="152" spans="1:10" ht="12.45">
+    <row r="152" spans="1:10">
       <c r="A152" s="41"/>
       <c r="B152" s="41"/>
       <c r="C152" s="41"/>
@@ -12950,7 +12842,7 @@
       <c r="I152" s="41"/>
       <c r="J152" s="41"/>
     </row>
-    <row r="153" spans="1:10" ht="12.45">
+    <row r="153" spans="1:10">
       <c r="A153" s="41"/>
       <c r="B153" s="41"/>
       <c r="C153" s="41"/>
@@ -12962,7 +12854,7 @@
       <c r="I153" s="41"/>
       <c r="J153" s="41"/>
     </row>
-    <row r="154" spans="1:10" ht="12.45">
+    <row r="154" spans="1:10">
       <c r="A154" s="41"/>
       <c r="B154" s="41"/>
       <c r="C154" s="41"/>
@@ -12974,7 +12866,7 @@
       <c r="I154" s="41"/>
       <c r="J154" s="41"/>
     </row>
-    <row r="155" spans="1:10" ht="12.45">
+    <row r="155" spans="1:10">
       <c r="A155" s="41"/>
       <c r="B155" s="41"/>
       <c r="C155" s="41"/>
@@ -12986,7 +12878,7 @@
       <c r="I155" s="41"/>
       <c r="J155" s="41"/>
     </row>
-    <row r="156" spans="1:10" ht="12.45">
+    <row r="156" spans="1:10">
       <c r="A156" s="41"/>
       <c r="B156" s="41"/>
       <c r="C156" s="41"/>
@@ -12998,7 +12890,7 @@
       <c r="I156" s="41"/>
       <c r="J156" s="41"/>
     </row>
-    <row r="157" spans="1:10" ht="12.45">
+    <row r="157" spans="1:10">
       <c r="A157" s="41"/>
       <c r="B157" s="41"/>
       <c r="C157" s="41"/>
@@ -13010,7 +12902,7 @@
       <c r="I157" s="41"/>
       <c r="J157" s="41"/>
     </row>
-    <row r="158" spans="1:10" ht="12.45">
+    <row r="158" spans="1:10">
       <c r="A158" s="41"/>
       <c r="B158" s="41"/>
       <c r="C158" s="41"/>
@@ -13022,7 +12914,7 @@
       <c r="I158" s="41"/>
       <c r="J158" s="41"/>
     </row>
-    <row r="159" spans="1:10" ht="12.45">
+    <row r="159" spans="1:10">
       <c r="A159" s="41"/>
       <c r="B159" s="41"/>
       <c r="C159" s="41"/>
@@ -13034,7 +12926,7 @@
       <c r="I159" s="41"/>
       <c r="J159" s="41"/>
     </row>
-    <row r="160" spans="1:10" ht="12.45">
+    <row r="160" spans="1:10">
       <c r="A160" s="41"/>
       <c r="B160" s="41"/>
       <c r="C160" s="41"/>
@@ -13046,7 +12938,7 @@
       <c r="I160" s="41"/>
       <c r="J160" s="41"/>
     </row>
-    <row r="161" spans="1:10" ht="12.45">
+    <row r="161" spans="1:10">
       <c r="A161" s="41"/>
       <c r="B161" s="41"/>
       <c r="C161" s="41"/>
@@ -13058,7 +12950,7 @@
       <c r="I161" s="41"/>
       <c r="J161" s="41"/>
     </row>
-    <row r="162" spans="1:10" ht="12.45">
+    <row r="162" spans="1:10">
       <c r="A162" s="41"/>
       <c r="B162" s="41"/>
       <c r="C162" s="41"/>
@@ -13070,7 +12962,7 @@
       <c r="I162" s="41"/>
       <c r="J162" s="41"/>
     </row>
-    <row r="163" spans="1:10" ht="12.45">
+    <row r="163" spans="1:10">
       <c r="A163" s="41"/>
       <c r="B163" s="41"/>
       <c r="C163" s="41"/>
@@ -13082,7 +12974,7 @@
       <c r="I163" s="41"/>
       <c r="J163" s="41"/>
     </row>
-    <row r="164" spans="1:10" ht="12.45">
+    <row r="164" spans="1:10">
       <c r="A164" s="41"/>
       <c r="B164" s="41"/>
       <c r="C164" s="41"/>
@@ -13094,7 +12986,7 @@
       <c r="I164" s="41"/>
       <c r="J164" s="41"/>
     </row>
-    <row r="165" spans="1:10" ht="12.45">
+    <row r="165" spans="1:10">
       <c r="A165" s="41"/>
       <c r="B165" s="41"/>
       <c r="C165" s="41"/>
@@ -13106,7 +12998,7 @@
       <c r="I165" s="41"/>
       <c r="J165" s="41"/>
     </row>
-    <row r="166" spans="1:10" ht="12.45">
+    <row r="166" spans="1:10">
       <c r="A166" s="41"/>
       <c r="B166" s="41"/>
       <c r="C166" s="41"/>
@@ -13118,7 +13010,7 @@
       <c r="I166" s="41"/>
       <c r="J166" s="41"/>
     </row>
-    <row r="167" spans="1:10" ht="12.45">
+    <row r="167" spans="1:10">
       <c r="A167" s="41"/>
       <c r="B167" s="41"/>
       <c r="C167" s="41"/>
@@ -13130,7 +13022,7 @@
       <c r="I167" s="41"/>
       <c r="J167" s="41"/>
     </row>
-    <row r="168" spans="1:10" ht="12.45">
+    <row r="168" spans="1:10">
       <c r="A168" s="41"/>
       <c r="B168" s="41"/>
       <c r="C168" s="41"/>
@@ -13142,7 +13034,7 @@
       <c r="I168" s="41"/>
       <c r="J168" s="41"/>
     </row>
-    <row r="169" spans="1:10" ht="12.45">
+    <row r="169" spans="1:10">
       <c r="A169" s="41"/>
       <c r="B169" s="41"/>
       <c r="C169" s="41"/>
@@ -13154,7 +13046,7 @@
       <c r="I169" s="41"/>
       <c r="J169" s="41"/>
     </row>
-    <row r="170" spans="1:10" ht="12.45">
+    <row r="170" spans="1:10">
       <c r="A170" s="41"/>
       <c r="B170" s="41"/>
       <c r="C170" s="41"/>
@@ -13166,7 +13058,7 @@
       <c r="I170" s="41"/>
       <c r="J170" s="41"/>
     </row>
-    <row r="171" spans="1:10" ht="12.45">
+    <row r="171" spans="1:10">
       <c r="A171" s="41"/>
       <c r="B171" s="41"/>
       <c r="C171" s="41"/>
@@ -13178,7 +13070,7 @@
       <c r="I171" s="41"/>
       <c r="J171" s="41"/>
     </row>
-    <row r="172" spans="1:10" ht="12.45">
+    <row r="172" spans="1:10">
       <c r="A172" s="41"/>
       <c r="B172" s="41"/>
       <c r="C172" s="41"/>
@@ -13190,7 +13082,7 @@
       <c r="I172" s="41"/>
       <c r="J172" s="41"/>
     </row>
-    <row r="173" spans="1:10" ht="12.45">
+    <row r="173" spans="1:10">
       <c r="A173" s="41"/>
       <c r="B173" s="41"/>
       <c r="C173" s="41"/>
@@ -13202,7 +13094,7 @@
       <c r="I173" s="41"/>
       <c r="J173" s="41"/>
     </row>
-    <row r="174" spans="1:10" ht="12.45">
+    <row r="174" spans="1:10">
       <c r="A174" s="41"/>
       <c r="B174" s="41"/>
       <c r="C174" s="41"/>
@@ -13214,7 +13106,7 @@
       <c r="I174" s="41"/>
       <c r="J174" s="41"/>
     </row>
-    <row r="175" spans="1:10" ht="12.45">
+    <row r="175" spans="1:10">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
       <c r="C175" s="41"/>
@@ -13226,7 +13118,7 @@
       <c r="I175" s="41"/>
       <c r="J175" s="41"/>
     </row>
-    <row r="176" spans="1:10" ht="12.45">
+    <row r="176" spans="1:10">
       <c r="A176" s="41"/>
       <c r="B176" s="41"/>
       <c r="C176" s="41"/>
@@ -13238,7 +13130,7 @@
       <c r="I176" s="41"/>
       <c r="J176" s="41"/>
     </row>
-    <row r="177" spans="1:10" ht="12.45">
+    <row r="177" spans="1:10">
       <c r="A177" s="41"/>
       <c r="B177" s="41"/>
       <c r="C177" s="41"/>
@@ -13250,7 +13142,7 @@
       <c r="I177" s="41"/>
       <c r="J177" s="41"/>
     </row>
-    <row r="178" spans="1:10" ht="12.45">
+    <row r="178" spans="1:10">
       <c r="A178" s="41"/>
       <c r="B178" s="41"/>
       <c r="C178" s="41"/>
@@ -13262,7 +13154,7 @@
       <c r="I178" s="41"/>
       <c r="J178" s="41"/>
     </row>
-    <row r="179" spans="1:10" ht="12.45">
+    <row r="179" spans="1:10">
       <c r="A179" s="41"/>
       <c r="B179" s="41"/>
       <c r="C179" s="41"/>
@@ -13274,7 +13166,7 @@
       <c r="I179" s="41"/>
       <c r="J179" s="41"/>
     </row>
-    <row r="180" spans="1:10" ht="12.45">
+    <row r="180" spans="1:10">
       <c r="A180" s="41"/>
       <c r="B180" s="41"/>
       <c r="C180" s="41"/>
@@ -13286,7 +13178,7 @@
       <c r="I180" s="41"/>
       <c r="J180" s="41"/>
     </row>
-    <row r="181" spans="1:10" ht="12.45">
+    <row r="181" spans="1:10">
       <c r="A181" s="41"/>
       <c r="B181" s="41"/>
       <c r="C181" s="41"/>
@@ -13298,7 +13190,7 @@
       <c r="I181" s="41"/>
       <c r="J181" s="41"/>
     </row>
-    <row r="182" spans="1:10" ht="12.45">
+    <row r="182" spans="1:10">
       <c r="A182" s="41"/>
       <c r="B182" s="41"/>
       <c r="C182" s="41"/>
@@ -13310,7 +13202,7 @@
       <c r="I182" s="41"/>
       <c r="J182" s="41"/>
     </row>
-    <row r="183" spans="1:10" ht="12.45">
+    <row r="183" spans="1:10">
       <c r="A183" s="41"/>
       <c r="B183" s="41"/>
       <c r="C183" s="41"/>
@@ -13322,7 +13214,7 @@
       <c r="I183" s="41"/>
       <c r="J183" s="41"/>
     </row>
-    <row r="184" spans="1:10" ht="12.45">
+    <row r="184" spans="1:10">
       <c r="A184" s="41"/>
       <c r="B184" s="41"/>
       <c r="C184" s="41"/>
@@ -13334,7 +13226,7 @@
       <c r="I184" s="41"/>
       <c r="J184" s="41"/>
     </row>
-    <row r="185" spans="1:10" ht="12.45">
+    <row r="185" spans="1:10">
       <c r="A185" s="41"/>
       <c r="B185" s="41"/>
       <c r="C185" s="41"/>
@@ -13346,7 +13238,7 @@
       <c r="I185" s="41"/>
       <c r="J185" s="41"/>
     </row>
-    <row r="186" spans="1:10" ht="12.45">
+    <row r="186" spans="1:10">
       <c r="A186" s="41"/>
       <c r="B186" s="41"/>
       <c r="C186" s="41"/>
@@ -13358,7 +13250,7 @@
       <c r="I186" s="41"/>
       <c r="J186" s="41"/>
     </row>
-    <row r="187" spans="1:10" ht="12.45">
+    <row r="187" spans="1:10">
       <c r="A187" s="41"/>
       <c r="B187" s="41"/>
       <c r="C187" s="41"/>
@@ -13370,7 +13262,7 @@
       <c r="I187" s="41"/>
       <c r="J187" s="41"/>
     </row>
-    <row r="188" spans="1:10" ht="12.45">
+    <row r="188" spans="1:10">
       <c r="A188" s="41"/>
       <c r="B188" s="41"/>
       <c r="C188" s="41"/>
@@ -13382,7 +13274,7 @@
       <c r="I188" s="41"/>
       <c r="J188" s="41"/>
     </row>
-    <row r="189" spans="1:10" ht="12.45">
+    <row r="189" spans="1:10">
       <c r="A189" s="41"/>
       <c r="B189" s="41"/>
       <c r="C189" s="41"/>
@@ -13394,7 +13286,7 @@
       <c r="I189" s="41"/>
       <c r="J189" s="41"/>
     </row>
-    <row r="190" spans="1:10" ht="12.45">
+    <row r="190" spans="1:10">
       <c r="A190" s="41"/>
       <c r="B190" s="41"/>
       <c r="C190" s="41"/>
@@ -13406,7 +13298,7 @@
       <c r="I190" s="41"/>
       <c r="J190" s="41"/>
     </row>
-    <row r="191" spans="1:10" ht="12.45">
+    <row r="191" spans="1:10">
       <c r="A191" s="41"/>
       <c r="B191" s="41"/>
       <c r="C191" s="41"/>
@@ -13418,7 +13310,7 @@
       <c r="I191" s="41"/>
       <c r="J191" s="41"/>
     </row>
-    <row r="192" spans="1:10" ht="12.45">
+    <row r="192" spans="1:10">
       <c r="A192" s="41"/>
       <c r="B192" s="41"/>
       <c r="C192" s="41"/>
@@ -13430,7 +13322,7 @@
       <c r="I192" s="41"/>
       <c r="J192" s="41"/>
     </row>
-    <row r="193" spans="1:10" ht="12.45">
+    <row r="193" spans="1:10">
       <c r="A193" s="41"/>
       <c r="B193" s="41"/>
       <c r="C193" s="41"/>
@@ -13442,7 +13334,7 @@
       <c r="I193" s="41"/>
       <c r="J193" s="41"/>
     </row>
-    <row r="194" spans="1:10" ht="12.45">
+    <row r="194" spans="1:10">
       <c r="A194" s="41"/>
       <c r="B194" s="41"/>
       <c r="C194" s="41"/>
@@ -13454,7 +13346,7 @@
       <c r="I194" s="41"/>
       <c r="J194" s="41"/>
     </row>
-    <row r="195" spans="1:10" ht="12.45">
+    <row r="195" spans="1:10">
       <c r="A195" s="41"/>
       <c r="B195" s="41"/>
       <c r="C195" s="41"/>
@@ -13466,7 +13358,7 @@
       <c r="I195" s="41"/>
       <c r="J195" s="41"/>
     </row>
-    <row r="196" spans="1:10" ht="12.45">
+    <row r="196" spans="1:10">
       <c r="A196" s="41"/>
       <c r="B196" s="41"/>
       <c r="C196" s="41"/>
@@ -13478,7 +13370,7 @@
       <c r="I196" s="41"/>
       <c r="J196" s="41"/>
     </row>
-    <row r="197" spans="1:10" ht="12.45">
+    <row r="197" spans="1:10">
       <c r="A197" s="41"/>
       <c r="B197" s="41"/>
       <c r="C197" s="41"/>
@@ -13490,7 +13382,7 @@
       <c r="I197" s="41"/>
       <c r="J197" s="41"/>
     </row>
-    <row r="198" spans="1:10" ht="12.45">
+    <row r="198" spans="1:10">
       <c r="A198" s="41"/>
       <c r="B198" s="41"/>
       <c r="C198" s="41"/>
@@ -13502,7 +13394,7 @@
       <c r="I198" s="41"/>
       <c r="J198" s="41"/>
     </row>
-    <row r="199" spans="1:10" ht="12.45">
+    <row r="199" spans="1:10">
       <c r="A199" s="41"/>
       <c r="B199" s="41"/>
       <c r="C199" s="41"/>
@@ -13514,7 +13406,7 @@
       <c r="I199" s="41"/>
       <c r="J199" s="41"/>
     </row>
-    <row r="200" spans="1:10" ht="12.45">
+    <row r="200" spans="1:10">
       <c r="A200" s="41"/>
       <c r="B200" s="41"/>
       <c r="C200" s="41"/>
@@ -13526,7 +13418,7 @@
       <c r="I200" s="41"/>
       <c r="J200" s="41"/>
     </row>
-    <row r="201" spans="1:10" ht="12.45">
+    <row r="201" spans="1:10">
       <c r="A201" s="41"/>
       <c r="B201" s="41"/>
       <c r="C201" s="41"/>
@@ -13538,7 +13430,7 @@
       <c r="I201" s="41"/>
       <c r="J201" s="41"/>
     </row>
-    <row r="202" spans="1:10" ht="12.45">
+    <row r="202" spans="1:10">
       <c r="A202" s="41"/>
       <c r="B202" s="41"/>
       <c r="C202" s="41"/>
@@ -13550,7 +13442,7 @@
       <c r="I202" s="41"/>
       <c r="J202" s="41"/>
     </row>
-    <row r="203" spans="1:10" ht="12.45">
+    <row r="203" spans="1:10">
       <c r="A203" s="41"/>
       <c r="B203" s="41"/>
       <c r="C203" s="41"/>
@@ -13562,7 +13454,7 @@
       <c r="I203" s="41"/>
       <c r="J203" s="41"/>
     </row>
-    <row r="204" spans="1:10" ht="12.45">
+    <row r="204" spans="1:10">
       <c r="A204" s="41"/>
       <c r="B204" s="41"/>
       <c r="C204" s="41"/>
@@ -13574,7 +13466,7 @@
       <c r="I204" s="41"/>
       <c r="J204" s="41"/>
     </row>
-    <row r="205" spans="1:10" ht="12.45">
+    <row r="205" spans="1:10">
       <c r="A205" s="41"/>
       <c r="B205" s="41"/>
       <c r="C205" s="41"/>
@@ -13586,7 +13478,7 @@
       <c r="I205" s="41"/>
       <c r="J205" s="41"/>
     </row>
-    <row r="206" spans="1:10" ht="12.45">
+    <row r="206" spans="1:10">
       <c r="A206" s="41"/>
       <c r="B206" s="41"/>
       <c r="C206" s="41"/>
@@ -13598,7 +13490,7 @@
       <c r="I206" s="41"/>
       <c r="J206" s="41"/>
     </row>
-    <row r="207" spans="1:10" ht="12.45">
+    <row r="207" spans="1:10">
       <c r="A207" s="41"/>
       <c r="B207" s="41"/>
       <c r="C207" s="41"/>
@@ -13610,7 +13502,7 @@
       <c r="I207" s="41"/>
       <c r="J207" s="41"/>
     </row>
-    <row r="208" spans="1:10" ht="12.45">
+    <row r="208" spans="1:10">
       <c r="A208" s="41"/>
       <c r="B208" s="41"/>
       <c r="C208" s="41"/>
